--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -1434,13 +1434,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.34480903935</v>
+        <v>46077.51147570602</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557081631945</v>
+        <v>46092.72374829861</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.617662488425</v>
+        <v>46118.784329155096</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1485,13 +1485,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.3448821875</v>
+        <v>46077.51154885416</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55704629629</v>
+        <v>46092.723712962965</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.73485108797</v>
+        <v>46133.901517754624</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1550,13 +1550,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.34488682871</v>
+        <v>46077.511553495366</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557046828704</v>
+        <v>46092.723713495376</v>
       </c>
       <c r="D6" s="5">
-        <v>46100.47969706019</v>
+        <v>46100.64636372685</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1615,13 +1615,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.34489075231</v>
+        <v>46077.511557418984</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55704726852</v>
+        <v>46092.723713935186</v>
       </c>
       <c r="D7" s="8">
-        <v>46100.47124013889</v>
+        <v>46100.637906805554</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
@@ -1680,13 +1680,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.344894444446</v>
+        <v>46077.51156111111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55704775463</v>
+        <v>46092.7237144213</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.52584615741</v>
+        <v>46100.69251282407</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1745,13 +1745,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.3448990162</v>
+        <v>46077.51156568287</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55704846064</v>
+        <v>46092.723715127315</v>
       </c>
       <c r="D9" s="8">
-        <v>46100.50993768519</v>
+        <v>46100.67660435185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
@@ -1810,13 +1810,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.34481357639</v>
+        <v>46077.511480243054</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.3602930787</v>
+        <v>46114.52695974537</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.360304699076</v>
+        <v>46114.52697136574</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -1863,13 +1863,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.34490351852</v>
+        <v>46077.51157018519</v>
       </c>
       <c r="C11" s="8">
-        <v>46100.477287430556</v>
+        <v>46100.64395409722</v>
       </c>
       <c r="D11" s="8">
-        <v>46100.477307152774</v>
+        <v>46100.643973819446</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -1928,13 +1928,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.34492337963</v>
+        <v>46077.5115900463</v>
       </c>
       <c r="C12" s="5">
-        <v>46100.47761854167</v>
+        <v>46100.644285208335</v>
       </c>
       <c r="D12" s="5">
-        <v>46100.52419221065</v>
+        <v>46100.690858877315</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -1993,13 +1993,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46077.34492927083</v>
+        <v>46077.511595937496</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36694313657</v>
+        <v>46097.53360980324</v>
       </c>
       <c r="D13" s="8">
-        <v>46101.65290020833</v>
+        <v>46101.819566875</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2058,13 +2058,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46077.344935601854</v>
+        <v>46077.51160226852</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.36027583333</v>
+        <v>46114.5269425</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.36029434028</v>
+        <v>46114.526961006944</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2123,13 +2123,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="8">
-        <v>46077.34481809028</v>
+        <v>46077.51148475695</v>
       </c>
       <c r="C15" s="8">
-        <v>46100.48517155093</v>
+        <v>46100.65183821759</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.48518900463</v>
+        <v>46100.6518556713</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2176,13 +2176,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46077.34494527778</v>
+        <v>46077.51161194444</v>
       </c>
       <c r="C16" s="5">
-        <v>46100.48473333333</v>
+        <v>46100.6514</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.495952233796</v>
+        <v>46181.66261890046</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2241,13 +2241,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.34495171296</v>
+        <v>46077.511618379634</v>
       </c>
       <c r="C17" s="8">
-        <v>46100.48430590278</v>
+        <v>46100.65097256945</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.485093634255</v>
+        <v>46100.65176030093</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2306,13 +2306,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.34495820602</v>
+        <v>46077.511624872684</v>
       </c>
       <c r="C18" s="5">
-        <v>46100.48515561342</v>
+        <v>46100.651822280095</v>
       </c>
       <c r="D18" s="5">
-        <v>46100.52274891204</v>
+        <v>46100.6894155787</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2371,13 +2371,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.34496451389</v>
+        <v>46077.511631180554</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36699548611</v>
+        <v>46097.53366215278</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.54238221065</v>
+        <v>46100.70904887731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>84</v>
@@ -2436,13 +2436,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.34482258101</v>
+        <v>46077.511489247685</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.41767866898</v>
+        <v>46181.58434533565</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.417680300925</v>
+        <v>46181.58434696759</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2485,13 +2485,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.34497618055</v>
+        <v>46077.511642847225</v>
       </c>
       <c r="C21" s="8">
-        <v>46104.42517269676</v>
+        <v>46104.59183936343</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.42518569445</v>
+        <v>46104.59185236111</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2550,13 +2550,13 @@
         <v>98</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.3449815625</v>
+        <v>46077.51164822916</v>
       </c>
       <c r="C22" s="5">
-        <v>46104.424802222224</v>
+        <v>46104.59146888889</v>
       </c>
       <c r="D22" s="5">
-        <v>46104.42480415509</v>
+        <v>46104.59147082176</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>99</v>
@@ -2611,13 +2611,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.344987372686</v>
+        <v>46077.51165403935</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.42515597222</v>
+        <v>46104.59182263889</v>
       </c>
       <c r="D23" s="8">
-        <v>46104.42515767361</v>
+        <v>46104.59182434028</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -2672,13 +2672,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.34499329861</v>
+        <v>46077.51165996528</v>
       </c>
       <c r="C24" s="5">
-        <v>46104.42693460648</v>
+        <v>46104.59360127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46104.42694795139</v>
+        <v>46104.593614618054</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -2737,13 +2737,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.34499914352</v>
+        <v>46077.51166581019</v>
       </c>
       <c r="C25" s="8">
-        <v>46104.42687686342</v>
+        <v>46104.59354353009</v>
       </c>
       <c r="D25" s="8">
-        <v>46104.42687885417</v>
+        <v>46104.59354552084</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2798,13 +2798,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.345004918985</v>
+        <v>46077.51167158565</v>
       </c>
       <c r="C26" s="5">
-        <v>46104.42691846065</v>
+        <v>46104.59358512731</v>
       </c>
       <c r="D26" s="5">
-        <v>46104.4269202662</v>
+        <v>46104.59358693287</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2859,13 +2859,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.345010613426</v>
+        <v>46077.5116772801</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.453170740744</v>
+        <v>46174.61983740741</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.49600302083</v>
+        <v>46181.6626696875</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -2924,13 +2924,13 @@
         <v>119</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.345068842595</v>
+        <v>46077.51173550926</v>
       </c>
       <c r="C28" s="5">
-        <v>46104.42801989583</v>
+        <v>46104.5946865625</v>
       </c>
       <c r="D28" s="5">
-        <v>46104.42802152778</v>
+        <v>46104.59468819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>120</v>
@@ -2985,13 +2985,13 @@
         <v>122</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.34507740741</v>
+        <v>46077.51174407407</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45263746528</v>
+        <v>46174.61930413195</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45263943287</v>
+        <v>46174.619306099536</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>123</v>
@@ -3046,13 +3046,13 @@
         <v>125</v>
       </c>
       <c r="B30" s="5">
-        <v>46077.34508395834</v>
+        <v>46077.511750624995</v>
       </c>
       <c r="C30" s="5">
-        <v>46127.61769663195</v>
+        <v>46127.78436329861</v>
       </c>
       <c r="D30" s="5">
-        <v>46127.61769806713</v>
+        <v>46127.7843647338</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>126</v>
@@ -3107,13 +3107,13 @@
         <v>128</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.34509065972</v>
+        <v>46077.511757326385</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.426340798615</v>
+        <v>46104.59300746528</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42635520833</v>
+        <v>46104.593021875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>129</v>
@@ -3172,13 +3172,13 @@
         <v>133</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.34509805556</v>
+        <v>46077.51176472222</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.36704096065</v>
+        <v>46097.53370762731</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.36704295139</v>
+        <v>46097.53370961806</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>134</v>
@@ -3233,13 +3233,13 @@
         <v>136</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.34511206018</v>
+        <v>46077.511778726854</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.42632423611</v>
+        <v>46104.59299090278</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.426325925924</v>
+        <v>46104.59299259259</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>137</v>
@@ -3294,13 +3294,13 @@
         <v>139</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.34482701389</v>
+        <v>46077.511493680555</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.41768997685</v>
+        <v>46181.58435664352</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.496130150466</v>
+        <v>46181.66279681713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>140</v>
@@ -3343,13 +3343,13 @@
         <v>142</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.34513821759</v>
+        <v>46077.511804884256</v>
       </c>
       <c r="C35" s="8">
-        <v>46098.351632488426</v>
+        <v>46098.5182991551</v>
       </c>
       <c r="D35" s="8">
-        <v>46098.35165217593</v>
+        <v>46098.51831884259</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>143</v>
@@ -3408,13 +3408,13 @@
         <v>147</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.34514715278</v>
+        <v>46077.511813819445</v>
       </c>
       <c r="C36" s="5">
-        <v>46132.43331230324</v>
+        <v>46132.59997896991</v>
       </c>
       <c r="D36" s="5">
-        <v>46132.43332836806</v>
+        <v>46132.59999503472</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>148</v>
@@ -3473,13 +3473,13 @@
         <v>151</v>
       </c>
       <c r="B37" s="8">
-        <v>46092.34842112269</v>
+        <v>46092.51508778935</v>
       </c>
       <c r="C37" s="8">
-        <v>46132.433354560184</v>
+        <v>46132.600021226855</v>
       </c>
       <c r="D37" s="8">
-        <v>46132.43336967593</v>
+        <v>46132.60003634259</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>152</v>
@@ -3538,13 +3538,13 @@
         <v>154</v>
       </c>
       <c r="B38" s="5">
-        <v>46092.34848678241</v>
+        <v>46092.51515344907</v>
       </c>
       <c r="C38" s="5">
-        <v>46181.41808329861</v>
+        <v>46181.584749965274</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.49616394676</v>
+        <v>46181.66283061342</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>155</v>
@@ -3603,13 +3603,13 @@
         <v>160</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.34515645834</v>
+        <v>46077.511823125</v>
       </c>
       <c r="C39" s="8">
-        <v>46181.41770111111</v>
+        <v>46181.584367777774</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.41770262731</v>
+        <v>46181.58436929398</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>161</v>
@@ -3652,13 +3652,13 @@
         <v>163</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.345161261575</v>
+        <v>46077.51182792824</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.41753746528</v>
+        <v>46181.58420413194</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.496286678244</v>
+        <v>46181.66295334491</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>164</v>
@@ -3717,13 +3717,13 @@
         <v>168</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.345176006944</v>
+        <v>46077.511842673615</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.36896997685</v>
+        <v>46147.535636643515</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.49628719907</v>
+        <v>46181.66295386574</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>169</v>
@@ -3782,13 +3782,13 @@
         <v>173</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.345182951394</v>
+        <v>46077.51184961805</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.41774614583</v>
+        <v>46181.5844128125</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.41774722222</v>
+        <v>46181.58441388889</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>174</v>
@@ -3831,13 +3831,13 @@
         <v>176</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.34518682871</v>
+        <v>46077.511853495365</v>
       </c>
       <c r="C43" s="8">
-        <v>46128.33537184028</v>
+        <v>46128.502038506944</v>
       </c>
       <c r="D43" s="8">
-        <v>46147.36897947917</v>
+        <v>46147.53564614583</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>177</v>
@@ -3896,13 +3896,13 @@
         <v>181</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.34519314815</v>
+        <v>46077.51185981481</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.42466203704</v>
+        <v>46146.591328703704</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.49643130787</v>
+        <v>46181.66309797454</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>182</v>
@@ -3961,13 +3961,13 @@
         <v>185</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.34520053241</v>
+        <v>46077.51186719908</v>
       </c>
       <c r="C45" s="8">
-        <v>46147.36925689815</v>
+        <v>46147.535923564814</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.496482013885</v>
+        <v>46181.663148680556</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>186</v>
@@ -4026,13 +4026,13 @@
         <v>189</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.34525758102</v>
+        <v>46077.51192424769</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.41777166667</v>
+        <v>46181.58443833333</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.41777292824</v>
+        <v>46181.58443959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>161</v>
@@ -4075,13 +4075,13 @@
         <v>191</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.345262523144</v>
+        <v>46077.511929189815</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.41758821759</v>
+        <v>46181.58425488426</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.49659675926</v>
+        <v>46181.66326342593</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>192</v>
@@ -4140,13 +4140,13 @@
         <v>194</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.34526938657</v>
+        <v>46077.51193605324</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.41759700231</v>
+        <v>46181.58426366898</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.49659732639</v>
+        <v>46181.663263993054</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>195</v>
@@ -4205,13 +4205,13 @@
         <v>197</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.3452759838</v>
+        <v>46077.51194265047</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.417601875</v>
+        <v>46181.58426854167</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.49659790509</v>
+        <v>46181.66326457176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>198</v>
@@ -4270,13 +4270,13 @@
         <v>200</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.34528774305</v>
+        <v>46077.511954409725</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.41913578704</v>
+        <v>46181.5858024537</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.41913684028</v>
+        <v>46181.58580350694</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>201</v>
@@ -4319,13 +4319,13 @@
         <v>203</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.34529165509</v>
+        <v>46077.51195832176</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.41761347222</v>
+        <v>46181.58428013889</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.49683065972</v>
+        <v>46181.663497326386</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>204</v>
@@ -4384,13 +4384,13 @@
         <v>206</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.34529802084</v>
+        <v>46077.511964687495</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.4178033912</v>
+        <v>46181.584470057875</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.49683127315</v>
+        <v>46181.663497939815</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>207</v>
@@ -4449,13 +4449,13 @@
         <v>210</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.34530688658</v>
+        <v>46077.511973553235</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.417811817126</v>
+        <v>46181.5844784838</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.49683184028</v>
+        <v>46181.66349850694</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>211</v>
@@ -4512,13 +4512,13 @@
         <v>213</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.345315266204</v>
+        <v>46077.51198193287</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.41781806713</v>
+        <v>46181.5844847338</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.49683244213</v>
+        <v>46181.66349910879</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>214</v>
@@ -4575,13 +4575,13 @@
         <v>216</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.345345891204</v>
+        <v>46077.51201255787</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.41824584491</v>
+        <v>46181.58491251158</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.496833032405</v>
+        <v>46181.663499699076</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>158</v>
@@ -4638,13 +4638,13 @@
         <v>219</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.34535454861</v>
+        <v>46077.512021215276</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.41817359954</v>
+        <v>46181.58484026621</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.496833599536</v>
+        <v>46181.66350026621</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>159</v>
@@ -4703,13 +4703,13 @@
         <v>221</v>
       </c>
       <c r="B57" s="8">
-        <v>46077.3453603588</v>
+        <v>46077.51202702546</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.419090787036</v>
+        <v>46181.58575745371</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.419092083335</v>
+        <v>46181.58575875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>222</v>
@@ -4752,13 +4752,13 @@
         <v>224</v>
       </c>
       <c r="B58" s="5">
-        <v>46077.34540680556</v>
+        <v>46077.51207347222</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.41830841435</v>
+        <v>46181.584975081016</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.49699332176</v>
+        <v>46181.66365998842</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>225</v>
@@ -4817,13 +4817,13 @@
         <v>228</v>
       </c>
       <c r="B59" s="8">
-        <v>46077.34541657407</v>
+        <v>46077.51208324074</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.418344618054</v>
+        <v>46181.585011284726</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.49699222222</v>
+        <v>46181.663658888894</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>229</v>
@@ -4882,13 +4882,13 @@
         <v>231</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.34542400463</v>
+        <v>46077.5120906713</v>
       </c>
       <c r="C60" s="5">
-        <v>46150.52857429398</v>
+        <v>46150.695240960646</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.4969927662</v>
+        <v>46181.663659432874</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>232</v>
@@ -4947,13 +4947,13 @@
         <v>234</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.34543148148</v>
+        <v>46077.512098148145</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.41832832176</v>
+        <v>46181.58499498843</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.496993877314</v>
+        <v>46181.663660543985</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>235</v>
@@ -5012,11 +5012,11 @@
         <v>237</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.345439756944</v>
+        <v>46077.512106423615</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46092.36657046297</v>
+        <v>46092.533237129624</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>238</v>
@@ -5059,11 +5059,11 @@
         <v>240</v>
       </c>
       <c r="B63" s="8">
-        <v>46077.34544462963</v>
+        <v>46077.512111296295</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46181.41833716435</v>
+        <v>46181.58500383102</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>241</v>
@@ -5122,11 +5122,11 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46077.34545173611</v>
+        <v>46077.51211840278</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.42832565973</v>
+        <v>46182.59499232639</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -1434,13 +1434,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.51147570602</v>
+        <v>46077.34480903935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72374829861</v>
+        <v>46092.557081631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.784329155096</v>
+        <v>46118.617662488425</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1485,13 +1485,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.51154885416</v>
+        <v>46077.3448821875</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.723712962965</v>
+        <v>46092.55704629629</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.901517754624</v>
+        <v>46133.73485108797</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1550,13 +1550,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.511553495366</v>
+        <v>46077.34488682871</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.723713495376</v>
+        <v>46092.557046828704</v>
       </c>
       <c r="D6" s="5">
-        <v>46100.64636372685</v>
+        <v>46100.47969706019</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1615,13 +1615,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.511557418984</v>
+        <v>46077.34489075231</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.723713935186</v>
+        <v>46092.55704726852</v>
       </c>
       <c r="D7" s="8">
-        <v>46100.637906805554</v>
+        <v>46100.47124013889</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
@@ -1680,13 +1680,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.51156111111</v>
+        <v>46077.344894444446</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.7237144213</v>
+        <v>46092.55704775463</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.69251282407</v>
+        <v>46100.52584615741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1745,13 +1745,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.51156568287</v>
+        <v>46077.3448990162</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.723715127315</v>
+        <v>46092.55704846064</v>
       </c>
       <c r="D9" s="8">
-        <v>46100.67660435185</v>
+        <v>46100.50993768519</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
@@ -1810,13 +1810,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.511480243054</v>
+        <v>46077.34481357639</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.52695974537</v>
+        <v>46114.3602930787</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.52697136574</v>
+        <v>46114.360304699076</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -1863,13 +1863,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.51157018519</v>
+        <v>46077.34490351852</v>
       </c>
       <c r="C11" s="8">
-        <v>46100.64395409722</v>
+        <v>46100.477287430556</v>
       </c>
       <c r="D11" s="8">
-        <v>46100.643973819446</v>
+        <v>46100.477307152774</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -1928,13 +1928,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.5115900463</v>
+        <v>46077.34492337963</v>
       </c>
       <c r="C12" s="5">
-        <v>46100.644285208335</v>
+        <v>46100.47761854167</v>
       </c>
       <c r="D12" s="5">
-        <v>46100.690858877315</v>
+        <v>46100.52419221065</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -1993,13 +1993,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46077.511595937496</v>
+        <v>46077.34492927083</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53360980324</v>
+        <v>46097.36694313657</v>
       </c>
       <c r="D13" s="8">
-        <v>46101.819566875</v>
+        <v>46101.65290020833</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2058,13 +2058,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46077.51160226852</v>
+        <v>46077.344935601854</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.5269425</v>
+        <v>46114.36027583333</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.526961006944</v>
+        <v>46114.36029434028</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2123,13 +2123,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="8">
-        <v>46077.51148475695</v>
+        <v>46077.34481809028</v>
       </c>
       <c r="C15" s="8">
-        <v>46100.65183821759</v>
+        <v>46100.48517155093</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.6518556713</v>
+        <v>46100.48518900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2176,13 +2176,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46077.51161194444</v>
+        <v>46077.34494527778</v>
       </c>
       <c r="C16" s="5">
-        <v>46100.6514</v>
+        <v>46100.48473333333</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.66261890046</v>
+        <v>46181.495952233796</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2241,13 +2241,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.511618379634</v>
+        <v>46077.34495171296</v>
       </c>
       <c r="C17" s="8">
-        <v>46100.65097256945</v>
+        <v>46100.48430590278</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.65176030093</v>
+        <v>46100.485093634255</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2306,13 +2306,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.511624872684</v>
+        <v>46077.34495820602</v>
       </c>
       <c r="C18" s="5">
-        <v>46100.651822280095</v>
+        <v>46100.48515561342</v>
       </c>
       <c r="D18" s="5">
-        <v>46100.6894155787</v>
+        <v>46100.52274891204</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2371,13 +2371,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.511631180554</v>
+        <v>46077.34496451389</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.53366215278</v>
+        <v>46097.36699548611</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.70904887731</v>
+        <v>46100.54238221065</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>84</v>
@@ -2436,13 +2436,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.511489247685</v>
+        <v>46077.34482258101</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.58434533565</v>
+        <v>46181.41767866898</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.58434696759</v>
+        <v>46181.417680300925</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2485,13 +2485,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.511642847225</v>
+        <v>46077.34497618055</v>
       </c>
       <c r="C21" s="8">
-        <v>46104.59183936343</v>
+        <v>46104.42517269676</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.59185236111</v>
+        <v>46104.42518569445</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2550,13 +2550,13 @@
         <v>98</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.51164822916</v>
+        <v>46077.3449815625</v>
       </c>
       <c r="C22" s="5">
-        <v>46104.59146888889</v>
+        <v>46104.424802222224</v>
       </c>
       <c r="D22" s="5">
-        <v>46104.59147082176</v>
+        <v>46104.42480415509</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>99</v>
@@ -2611,13 +2611,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.51165403935</v>
+        <v>46077.344987372686</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.59182263889</v>
+        <v>46104.42515597222</v>
       </c>
       <c r="D23" s="8">
-        <v>46104.59182434028</v>
+        <v>46104.42515767361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -2672,13 +2672,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.51165996528</v>
+        <v>46077.34499329861</v>
       </c>
       <c r="C24" s="5">
-        <v>46104.59360127315</v>
+        <v>46104.42693460648</v>
       </c>
       <c r="D24" s="5">
-        <v>46104.593614618054</v>
+        <v>46104.42694795139</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -2737,13 +2737,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.51166581019</v>
+        <v>46077.34499914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46104.59354353009</v>
+        <v>46104.42687686342</v>
       </c>
       <c r="D25" s="8">
-        <v>46104.59354552084</v>
+        <v>46104.42687885417</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -2798,13 +2798,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.51167158565</v>
+        <v>46077.345004918985</v>
       </c>
       <c r="C26" s="5">
-        <v>46104.59358512731</v>
+        <v>46104.42691846065</v>
       </c>
       <c r="D26" s="5">
-        <v>46104.59358693287</v>
+        <v>46104.4269202662</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -2859,13 +2859,13 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.5116772801</v>
+        <v>46077.345010613426</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.61983740741</v>
+        <v>46174.453170740744</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.6626696875</v>
+        <v>46181.49600302083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -2924,13 +2924,13 @@
         <v>119</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.51173550926</v>
+        <v>46077.345068842595</v>
       </c>
       <c r="C28" s="5">
-        <v>46104.5946865625</v>
+        <v>46104.42801989583</v>
       </c>
       <c r="D28" s="5">
-        <v>46104.59468819444</v>
+        <v>46104.42802152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>120</v>
@@ -2985,13 +2985,13 @@
         <v>122</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.51174407407</v>
+        <v>46077.34507740741</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.61930413195</v>
+        <v>46174.45263746528</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.619306099536</v>
+        <v>46174.45263943287</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>123</v>
@@ -3046,13 +3046,13 @@
         <v>125</v>
       </c>
       <c r="B30" s="5">
-        <v>46077.511750624995</v>
+        <v>46077.34508395834</v>
       </c>
       <c r="C30" s="5">
-        <v>46127.78436329861</v>
+        <v>46127.61769663195</v>
       </c>
       <c r="D30" s="5">
-        <v>46127.7843647338</v>
+        <v>46127.61769806713</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>126</v>
@@ -3107,13 +3107,13 @@
         <v>128</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.511757326385</v>
+        <v>46077.34509065972</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.59300746528</v>
+        <v>46104.426340798615</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.593021875</v>
+        <v>46104.42635520833</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>129</v>
@@ -3172,13 +3172,13 @@
         <v>133</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.51176472222</v>
+        <v>46077.34509805556</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53370762731</v>
+        <v>46097.36704096065</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.53370961806</v>
+        <v>46097.36704295139</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>134</v>
@@ -3233,13 +3233,13 @@
         <v>136</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.511778726854</v>
+        <v>46077.34511206018</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.59299090278</v>
+        <v>46104.42632423611</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.59299259259</v>
+        <v>46104.426325925924</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>137</v>
@@ -3294,13 +3294,13 @@
         <v>139</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.511493680555</v>
+        <v>46077.34482701389</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.58435664352</v>
+        <v>46181.41768997685</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.66279681713</v>
+        <v>46181.496130150466</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>140</v>
@@ -3343,13 +3343,13 @@
         <v>142</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.511804884256</v>
+        <v>46077.34513821759</v>
       </c>
       <c r="C35" s="8">
-        <v>46098.5182991551</v>
+        <v>46098.351632488426</v>
       </c>
       <c r="D35" s="8">
-        <v>46098.51831884259</v>
+        <v>46098.35165217593</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>143</v>
@@ -3408,13 +3408,13 @@
         <v>147</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.511813819445</v>
+        <v>46077.34514715278</v>
       </c>
       <c r="C36" s="5">
-        <v>46132.59997896991</v>
+        <v>46132.43331230324</v>
       </c>
       <c r="D36" s="5">
-        <v>46132.59999503472</v>
+        <v>46132.43332836806</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>148</v>
@@ -3473,13 +3473,13 @@
         <v>151</v>
       </c>
       <c r="B37" s="8">
-        <v>46092.51508778935</v>
+        <v>46092.34842112269</v>
       </c>
       <c r="C37" s="8">
-        <v>46132.600021226855</v>
+        <v>46132.433354560184</v>
       </c>
       <c r="D37" s="8">
-        <v>46132.60003634259</v>
+        <v>46132.43336967593</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>152</v>
@@ -3538,13 +3538,13 @@
         <v>154</v>
       </c>
       <c r="B38" s="5">
-        <v>46092.51515344907</v>
+        <v>46092.34848678241</v>
       </c>
       <c r="C38" s="5">
-        <v>46181.584749965274</v>
+        <v>46181.41808329861</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.66283061342</v>
+        <v>46181.49616394676</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>155</v>
@@ -3603,13 +3603,13 @@
         <v>160</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.511823125</v>
+        <v>46077.34515645834</v>
       </c>
       <c r="C39" s="8">
-        <v>46181.584367777774</v>
+        <v>46181.41770111111</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.58436929398</v>
+        <v>46181.41770262731</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>161</v>
@@ -3652,13 +3652,13 @@
         <v>163</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.51182792824</v>
+        <v>46077.345161261575</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.58420413194</v>
+        <v>46181.41753746528</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.66295334491</v>
+        <v>46181.496286678244</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>164</v>
@@ -3717,13 +3717,13 @@
         <v>168</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.511842673615</v>
+        <v>46077.345176006944</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.535636643515</v>
+        <v>46147.36896997685</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.66295386574</v>
+        <v>46181.49628719907</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>169</v>
@@ -3782,13 +3782,13 @@
         <v>173</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.51184961805</v>
+        <v>46077.345182951394</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.5844128125</v>
+        <v>46181.41774614583</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.58441388889</v>
+        <v>46181.41774722222</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>174</v>
@@ -3831,13 +3831,13 @@
         <v>176</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.511853495365</v>
+        <v>46077.34518682871</v>
       </c>
       <c r="C43" s="8">
-        <v>46128.502038506944</v>
+        <v>46128.33537184028</v>
       </c>
       <c r="D43" s="8">
-        <v>46147.53564614583</v>
+        <v>46147.36897947917</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>177</v>
@@ -3896,13 +3896,13 @@
         <v>181</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.51185981481</v>
+        <v>46077.34519314815</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.591328703704</v>
+        <v>46146.42466203704</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66309797454</v>
+        <v>46181.49643130787</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>182</v>
@@ -3961,13 +3961,13 @@
         <v>185</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.51186719908</v>
+        <v>46077.34520053241</v>
       </c>
       <c r="C45" s="8">
-        <v>46147.535923564814</v>
+        <v>46147.36925689815</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.663148680556</v>
+        <v>46181.496482013885</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>186</v>
@@ -4026,13 +4026,13 @@
         <v>189</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.51192424769</v>
+        <v>46077.34525758102</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.58443833333</v>
+        <v>46181.41777166667</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.58443959491</v>
+        <v>46181.41777292824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>161</v>
@@ -4075,13 +4075,13 @@
         <v>191</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.511929189815</v>
+        <v>46077.345262523144</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.58425488426</v>
+        <v>46181.41758821759</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66326342593</v>
+        <v>46181.49659675926</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>192</v>
@@ -4140,13 +4140,13 @@
         <v>194</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.51193605324</v>
+        <v>46077.34526938657</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.58426366898</v>
+        <v>46181.41759700231</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.663263993054</v>
+        <v>46181.49659732639</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>195</v>
@@ -4205,13 +4205,13 @@
         <v>197</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.51194265047</v>
+        <v>46077.3452759838</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.58426854167</v>
+        <v>46181.417601875</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66326457176</v>
+        <v>46181.49659790509</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>198</v>
@@ -4270,13 +4270,13 @@
         <v>200</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.511954409725</v>
+        <v>46077.34528774305</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.5858024537</v>
+        <v>46181.41913578704</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.58580350694</v>
+        <v>46181.41913684028</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>201</v>
@@ -4319,13 +4319,13 @@
         <v>203</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.51195832176</v>
+        <v>46077.34529165509</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.58428013889</v>
+        <v>46181.41761347222</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.663497326386</v>
+        <v>46181.49683065972</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>204</v>
@@ -4384,13 +4384,13 @@
         <v>206</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.511964687495</v>
+        <v>46077.34529802084</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.584470057875</v>
+        <v>46181.4178033912</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.663497939815</v>
+        <v>46181.49683127315</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>207</v>
@@ -4449,13 +4449,13 @@
         <v>210</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.511973553235</v>
+        <v>46077.34530688658</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.5844784838</v>
+        <v>46181.417811817126</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.66349850694</v>
+        <v>46181.49683184028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>211</v>
@@ -4512,13 +4512,13 @@
         <v>213</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.51198193287</v>
+        <v>46077.345315266204</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.5844847338</v>
+        <v>46181.41781806713</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.66349910879</v>
+        <v>46181.49683244213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>214</v>
@@ -4575,13 +4575,13 @@
         <v>216</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.51201255787</v>
+        <v>46077.345345891204</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.58491251158</v>
+        <v>46181.41824584491</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.663499699076</v>
+        <v>46181.496833032405</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>158</v>
@@ -4638,13 +4638,13 @@
         <v>219</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.512021215276</v>
+        <v>46077.34535454861</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.58484026621</v>
+        <v>46181.41817359954</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.66350026621</v>
+        <v>46181.496833599536</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>159</v>
@@ -4703,13 +4703,13 @@
         <v>221</v>
       </c>
       <c r="B57" s="8">
-        <v>46077.51202702546</v>
+        <v>46077.3453603588</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.58575745371</v>
+        <v>46181.419090787036</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.58575875</v>
+        <v>46181.419092083335</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>222</v>
@@ -4752,13 +4752,13 @@
         <v>224</v>
       </c>
       <c r="B58" s="5">
-        <v>46077.51207347222</v>
+        <v>46077.34540680556</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.584975081016</v>
+        <v>46181.41830841435</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.66365998842</v>
+        <v>46181.49699332176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>225</v>
@@ -4817,13 +4817,13 @@
         <v>228</v>
       </c>
       <c r="B59" s="8">
-        <v>46077.51208324074</v>
+        <v>46077.34541657407</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.585011284726</v>
+        <v>46181.418344618054</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.663658888894</v>
+        <v>46181.49699222222</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>229</v>
@@ -4882,13 +4882,13 @@
         <v>231</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.5120906713</v>
+        <v>46077.34542400463</v>
       </c>
       <c r="C60" s="5">
-        <v>46150.695240960646</v>
+        <v>46150.52857429398</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.663659432874</v>
+        <v>46181.4969927662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>232</v>
@@ -4947,13 +4947,13 @@
         <v>234</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.512098148145</v>
+        <v>46077.34543148148</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.58499498843</v>
+        <v>46181.41832832176</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.663660543985</v>
+        <v>46181.496993877314</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>235</v>
@@ -5012,11 +5012,11 @@
         <v>237</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.512106423615</v>
+        <v>46077.345439756944</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46092.533237129624</v>
+        <v>46092.36657046297</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>238</v>
@@ -5059,11 +5059,11 @@
         <v>240</v>
       </c>
       <c r="B63" s="8">
-        <v>46077.512111296295</v>
+        <v>46077.34544462963</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46181.58500383102</v>
+        <v>46181.41833716435</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>241</v>
@@ -5122,11 +5122,11 @@
         <v>244</v>
       </c>
       <c r="B64" s="5">
-        <v>46077.51211840278</v>
+        <v>46077.34545173611</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.59499232639</v>
+        <v>46182.42832565973</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>245</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="244">
   <si>
     <t xml:space="preserve"> 50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -306,9 +306,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rodete de placas s/plano 4999.00
 Z8 N590
 Primer rodete con calaje -6°, segundo rodete con calaje -7°
@@ -322,12 +319,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">Alabe s/ plano 4999.01 de Código 300000
@@ -2321,11 +2312,9 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46022</v>
       </c>
@@ -2336,7 +2325,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2348,7 +2337,7 @@
         <v>57</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46022</v>
@@ -2368,7 +2357,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46077.511631180554</v>
@@ -2380,17 +2369,15 @@
         <v>46100.70904887731</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46024</v>
       </c>
@@ -2401,7 +2388,7 @@
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
@@ -2413,7 +2400,7 @@
         <v>61</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="8">
         <v>46024</v>
@@ -2433,7 +2420,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46077.511489247685</v>
@@ -2445,7 +2432,7 @@
         <v>46181.58434696759</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2469,7 +2456,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2482,7 +2469,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8">
         <v>46077.511642847225</v>
@@ -2494,16 +2481,16 @@
         <v>46104.59185236111</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8">
         <v>46027</v>
@@ -2515,19 +2502,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46027</v>
@@ -2547,7 +2534,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5">
         <v>46077.51164822916</v>
@@ -2559,16 +2546,16 @@
         <v>46104.59147082176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I22" s="5">
         <v>46027</v>
@@ -2586,29 +2573,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>46077.51165403935</v>
@@ -2620,16 +2607,16 @@
         <v>46104.59182434028</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I23" s="8">
         <v>46029</v>
@@ -2647,29 +2634,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46077.51165996528</v>
@@ -2681,16 +2668,16 @@
         <v>46104.593614618054</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I24" s="5">
         <v>46027</v>
@@ -2708,13 +2695,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q24" s="5">
         <v>46027</v>
@@ -2734,7 +2721,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B25" s="8">
         <v>46077.51166581019</v>
@@ -2746,16 +2733,16 @@
         <v>46104.59354552084</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I25" s="8">
         <v>46027</v>
@@ -2773,29 +2760,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46077.51167158565</v>
@@ -2807,16 +2794,16 @@
         <v>46104.59358693287</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I26" s="5">
         <v>46029</v>
@@ -2834,29 +2821,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="O26" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="P26" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B27" s="8">
         <v>46077.5116772801</v>
@@ -2868,16 +2855,16 @@
         <v>46181.6626696875</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -2889,19 +2876,19 @@
         <v>26</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -2921,7 +2908,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5">
         <v>46077.51173550926</v>
@@ -2933,16 +2920,16 @@
         <v>46104.59468819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -2960,29 +2947,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B29" s="8">
         <v>46077.51174407407</v>
@@ -2994,16 +2981,16 @@
         <v>46174.619306099536</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I29" s="8">
         <v>46036</v>
@@ -3021,29 +3008,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B30" s="5">
         <v>46077.511750624995</v>
@@ -3055,16 +3042,16 @@
         <v>46127.7843647338</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I30" s="5">
         <v>46036</v>
@@ -3082,29 +3069,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B31" s="8">
         <v>46077.511757326385</v>
@@ -3116,16 +3103,16 @@
         <v>46104.593021875</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I31" s="8">
         <v>46028</v>
@@ -3143,13 +3130,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q31" s="8">
         <v>46028</v>
@@ -3169,7 +3156,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46077.51176472222</v>
@@ -3181,16 +3168,16 @@
         <v>46097.53370961806</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I32" s="5">
         <v>46028</v>
@@ -3208,29 +3195,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B33" s="8">
         <v>46077.511778726854</v>
@@ -3242,16 +3229,16 @@
         <v>46104.59299259259</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I33" s="8">
         <v>46037</v>
@@ -3269,29 +3256,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46077.511493680555</v>
@@ -3303,7 +3290,7 @@
         <v>46181.66279681713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3327,7 +3314,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3340,7 +3327,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B35" s="8">
         <v>46077.511804884256</v>
@@ -3352,16 +3339,16 @@
         <v>46098.51831884259</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I35" s="8">
         <v>46024</v>
@@ -3379,13 +3366,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>61</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q35" s="8">
         <v>46024</v>
@@ -3405,7 +3392,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B36" s="5">
         <v>46077.511813819445</v>
@@ -3417,16 +3404,16 @@
         <v>46132.59999503472</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I36" s="5">
         <v>46045</v>
@@ -3444,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q36" s="5">
         <v>46045</v>
@@ -3470,7 +3457,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B37" s="8">
         <v>46092.51508778935</v>
@@ -3482,16 +3469,16 @@
         <v>46132.60003634259</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3509,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q37" s="8">
         <v>46052</v>
@@ -3535,7 +3522,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B38" s="5">
         <v>46092.51515344907</v>
@@ -3547,16 +3534,16 @@
         <v>46181.66283061342</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I38" s="5">
         <v>46087</v>
@@ -3574,13 +3561,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q38" s="5">
         <v>46087</v>
@@ -3600,7 +3587,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B39" s="8">
         <v>46077.511823125</v>
@@ -3612,7 +3599,7 @@
         <v>46181.58436929398</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3636,7 +3623,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3649,7 +3636,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B40" s="5">
         <v>46077.51182792824</v>
@@ -3661,16 +3648,16 @@
         <v>46181.66295334491</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I40" s="5">
         <v>46057</v>
@@ -3688,13 +3675,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q40" s="5">
         <v>46057</v>
@@ -3714,7 +3701,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B41" s="8">
         <v>46077.511842673615</v>
@@ -3726,16 +3713,16 @@
         <v>46181.66295386574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I41" s="8">
         <v>46059</v>
@@ -3753,13 +3740,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q41" s="8">
         <v>46059</v>
@@ -3779,7 +3766,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B42" s="5">
         <v>46077.51184961805</v>
@@ -3791,7 +3778,7 @@
         <v>46181.58441388889</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3815,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3828,7 +3815,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B43" s="8">
         <v>46077.511853495365</v>
@@ -3840,16 +3827,16 @@
         <v>46147.53564614583</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I43" s="8">
         <v>46063</v>
@@ -3867,13 +3854,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q43" s="8">
         <v>46063</v>
@@ -3893,7 +3880,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B44" s="5">
         <v>46077.51185981481</v>
@@ -3905,16 +3892,16 @@
         <v>46181.66309797454</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I44" s="5">
         <v>46066</v>
@@ -3932,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q44" s="5">
         <v>46066</v>
@@ -3947,7 +3934,7 @@
         <v>46072</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -3958,7 +3945,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B45" s="8">
         <v>46077.51186719908</v>
@@ -3970,16 +3957,16 @@
         <v>46181.663148680556</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I45" s="8">
         <v>46073</v>
@@ -3997,13 +3984,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q45" s="8">
         <v>46073</v>
@@ -4023,7 +4010,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B46" s="5">
         <v>46077.51192424769</v>
@@ -4035,7 +4022,7 @@
         <v>46181.58443959491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4059,7 +4046,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4072,7 +4059,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B47" s="8">
         <v>46077.511929189815</v>
@@ -4084,16 +4071,16 @@
         <v>46181.66326342593</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I47" s="8">
         <v>46049</v>
@@ -4111,13 +4098,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q47" s="8">
         <v>46048</v>
@@ -4137,7 +4124,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B48" s="5">
         <v>46077.51193605324</v>
@@ -4149,16 +4136,16 @@
         <v>46181.663263993054</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46031</v>
@@ -4176,13 +4163,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q48" s="5">
         <v>46031</v>
@@ -4202,7 +4189,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B49" s="8">
         <v>46077.51194265047</v>
@@ -4214,16 +4201,16 @@
         <v>46181.66326457176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I49" s="8">
         <v>46065</v>
@@ -4241,13 +4228,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q49" s="8">
         <v>46065</v>
@@ -4267,7 +4254,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B50" s="5">
         <v>46077.511954409725</v>
@@ -4279,7 +4266,7 @@
         <v>46181.58580350694</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4303,7 +4290,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4316,7 +4303,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B51" s="8">
         <v>46077.51195832176</v>
@@ -4328,17 +4315,15 @@
         <v>46181.663497326386</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H51" s="9"/>
       <c r="I51" s="8">
         <v>46076</v>
       </c>
@@ -4355,13 +4340,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q51" s="8">
         <v>46076</v>
@@ -4381,7 +4366,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B52" s="5">
         <v>46077.511964687495</v>
@@ -4393,17 +4378,15 @@
         <v>46181.663497939815</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H52" s="6"/>
       <c r="I52" s="5">
         <v>46083</v>
       </c>
@@ -4420,13 +4403,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4446,7 +4429,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B53" s="8">
         <v>46077.511973553235</v>
@@ -4458,17 +4441,15 @@
         <v>46181.66349850694</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H53" s="9"/>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
         <v>46084</v>
@@ -4483,13 +4464,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q53" s="8">
         <v>46084</v>
@@ -4509,7 +4490,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B54" s="5">
         <v>46077.51198193287</v>
@@ -4521,17 +4502,15 @@
         <v>46181.66349910879</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
         <v>46085</v>
@@ -4546,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4572,7 +4551,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B55" s="8">
         <v>46077.51201255787</v>
@@ -4584,17 +4563,15 @@
         <v>46181.663499699076</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H55" s="9"/>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
         <v>46086</v>
@@ -4609,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4635,7 +4612,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B56" s="5">
         <v>46077.512021215276</v>
@@ -4647,17 +4624,15 @@
         <v>46181.66350026621</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
       <c r="I56" s="5">
         <v>46090</v>
       </c>
@@ -4674,13 +4649,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q56" s="5">
         <v>46090</v>
@@ -4700,7 +4675,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B57" s="8">
         <v>46077.51202702546</v>
@@ -4712,7 +4687,7 @@
         <v>46181.58575875</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4736,7 +4711,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4749,7 +4724,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B58" s="5">
         <v>46077.51207347222</v>
@@ -4761,7 +4736,7 @@
         <v>46181.66365998842</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4782,19 +4757,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q58" s="5">
         <v>46091</v>
@@ -4814,7 +4789,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B59" s="8">
         <v>46077.51208324074</v>
@@ -4826,17 +4801,15 @@
         <v>46181.663658888894</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="9"/>
       <c r="I59" s="8">
         <v>46092</v>
       </c>
@@ -4853,13 +4826,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="O59" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="O59" s="9" t="s">
-        <v>225</v>
-      </c>
       <c r="P59" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q59" s="8">
         <v>46092</v>
@@ -4879,7 +4852,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B60" s="5">
         <v>46077.5120906713</v>
@@ -4891,16 +4864,16 @@
         <v>46181.663659432874</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I60" s="5">
         <v>46093</v>
@@ -4918,13 +4891,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q60" s="5">
         <v>46093</v>
@@ -4944,7 +4917,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B61" s="8">
         <v>46077.512098148145</v>
@@ -4956,16 +4929,16 @@
         <v>46181.663660543985</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I61" s="8">
         <v>46094</v>
@@ -4983,13 +4956,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q61" s="8">
         <v>46094</v>
@@ -5009,7 +4982,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B62" s="5">
         <v>46077.512106423615</v>
@@ -5019,7 +4992,7 @@
         <v>46092.533237129624</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5043,7 +5016,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5056,7 +5029,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B63" s="8">
         <v>46077.512111296295</v>
@@ -5066,16 +5039,16 @@
         <v>46181.58500383102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I63" s="8">
         <v>46097</v>
@@ -5093,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="Q63" s="8">
         <v>46085</v>
@@ -5114,12 +5087,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B64" s="5">
         <v>46077.51211840278</v>
@@ -5129,16 +5102,16 @@
         <v>46182.59499232639</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I64" s="5">
         <v>46097</v>
@@ -5156,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q64" s="5">
         <v>46085</v>
@@ -5177,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="245">
   <si>
     <t xml:space="preserve"> 50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">Rodete de placas s/plano 4999.00
@@ -2303,7 +2306,7 @@
         <v>46100.651822280095</v>
       </c>
       <c r="D18" s="5">
-        <v>46100.6894155787</v>
+        <v>46223.81906920139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2312,9 +2315,11 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="I18" s="5">
         <v>46022</v>
       </c>
@@ -2325,7 +2330,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2337,7 +2342,7 @@
         <v>57</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46022</v>
@@ -2357,7 +2362,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="8">
         <v>46077.511631180554</v>
@@ -2366,18 +2371,20 @@
         <v>46097.53366215278</v>
       </c>
       <c r="D19" s="8">
-        <v>46100.70904887731</v>
+        <v>46223.81906576389</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="I19" s="8">
         <v>46024</v>
       </c>
@@ -2388,7 +2395,7 @@
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
@@ -2400,7 +2407,7 @@
         <v>61</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="8">
         <v>46024</v>
@@ -2420,7 +2427,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46077.511489247685</v>
@@ -2432,7 +2439,7 @@
         <v>46181.58434696759</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2456,7 +2463,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2469,7 +2476,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="8">
         <v>46077.511642847225</v>
@@ -2481,16 +2488,16 @@
         <v>46104.59185236111</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="8">
         <v>46027</v>
@@ -2502,19 +2509,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46027</v>
@@ -2534,7 +2541,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>46077.51164822916</v>
@@ -2546,16 +2553,16 @@
         <v>46104.59147082176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I22" s="5">
         <v>46027</v>
@@ -2573,29 +2580,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8">
         <v>46077.51165403935</v>
@@ -2607,16 +2614,16 @@
         <v>46104.59182434028</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" s="8">
         <v>46029</v>
@@ -2634,29 +2641,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="5">
         <v>46077.51165996528</v>
@@ -2668,16 +2675,16 @@
         <v>46104.593614618054</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I24" s="5">
         <v>46027</v>
@@ -2695,13 +2702,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q24" s="5">
         <v>46027</v>
@@ -2721,7 +2728,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="8">
         <v>46077.51166581019</v>
@@ -2733,16 +2740,16 @@
         <v>46104.59354552084</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="8">
         <v>46027</v>
@@ -2760,29 +2767,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>46077.51167158565</v>
@@ -2794,16 +2801,16 @@
         <v>46104.59358693287</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5">
         <v>46029</v>
@@ -2821,29 +2828,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="8">
         <v>46077.5116772801</v>
@@ -2855,16 +2862,16 @@
         <v>46181.6626696875</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -2876,19 +2883,19 @@
         <v>26</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -2908,7 +2915,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46077.51173550926</v>
@@ -2920,16 +2927,16 @@
         <v>46104.59468819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -2947,29 +2954,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8">
         <v>46077.51174407407</v>
@@ -2981,16 +2988,16 @@
         <v>46174.619306099536</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I29" s="8">
         <v>46036</v>
@@ -3008,29 +3015,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46077.511750624995</v>
@@ -3042,16 +3049,16 @@
         <v>46127.7843647338</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I30" s="5">
         <v>46036</v>
@@ -3069,29 +3076,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="8">
         <v>46077.511757326385</v>
@@ -3103,16 +3110,16 @@
         <v>46104.593021875</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I31" s="8">
         <v>46028</v>
@@ -3130,13 +3137,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q31" s="8">
         <v>46028</v>
@@ -3156,7 +3163,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5">
         <v>46077.51176472222</v>
@@ -3168,16 +3175,16 @@
         <v>46097.53370961806</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I32" s="5">
         <v>46028</v>
@@ -3195,29 +3202,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="8">
         <v>46077.511778726854</v>
@@ -3229,16 +3236,16 @@
         <v>46104.59299259259</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46037</v>
@@ -3256,29 +3263,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5">
         <v>46077.511493680555</v>
@@ -3290,7 +3297,7 @@
         <v>46181.66279681713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3314,7 +3321,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3327,7 +3334,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="8">
         <v>46077.511804884256</v>
@@ -3339,16 +3346,16 @@
         <v>46098.51831884259</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I35" s="8">
         <v>46024</v>
@@ -3366,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>61</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q35" s="8">
         <v>46024</v>
@@ -3392,7 +3399,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B36" s="5">
         <v>46077.511813819445</v>
@@ -3404,16 +3411,16 @@
         <v>46132.59999503472</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I36" s="5">
         <v>46045</v>
@@ -3431,13 +3438,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q36" s="5">
         <v>46045</v>
@@ -3457,7 +3464,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B37" s="8">
         <v>46092.51508778935</v>
@@ -3469,16 +3476,16 @@
         <v>46132.60003634259</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3496,13 +3503,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q37" s="8">
         <v>46052</v>
@@ -3522,7 +3529,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B38" s="5">
         <v>46092.51515344907</v>
@@ -3534,16 +3541,16 @@
         <v>46181.66283061342</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I38" s="5">
         <v>46087</v>
@@ -3561,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q38" s="5">
         <v>46087</v>
@@ -3587,7 +3594,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B39" s="8">
         <v>46077.511823125</v>
@@ -3599,7 +3606,7 @@
         <v>46181.58436929398</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3623,7 +3630,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3636,7 +3643,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B40" s="5">
         <v>46077.51182792824</v>
@@ -3648,16 +3655,16 @@
         <v>46181.66295334491</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I40" s="5">
         <v>46057</v>
@@ -3675,13 +3682,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q40" s="5">
         <v>46057</v>
@@ -3701,7 +3708,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B41" s="8">
         <v>46077.511842673615</v>
@@ -3713,16 +3720,16 @@
         <v>46181.66295386574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I41" s="8">
         <v>46059</v>
@@ -3740,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q41" s="8">
         <v>46059</v>
@@ -3766,7 +3773,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B42" s="5">
         <v>46077.51184961805</v>
@@ -3778,7 +3785,7 @@
         <v>46181.58441388889</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3802,7 +3809,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3815,7 +3822,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B43" s="8">
         <v>46077.511853495365</v>
@@ -3827,16 +3834,16 @@
         <v>46147.53564614583</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I43" s="8">
         <v>46063</v>
@@ -3854,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q43" s="8">
         <v>46063</v>
@@ -3880,7 +3887,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B44" s="5">
         <v>46077.51185981481</v>
@@ -3892,16 +3899,16 @@
         <v>46181.66309797454</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I44" s="5">
         <v>46066</v>
@@ -3919,13 +3926,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q44" s="5">
         <v>46066</v>
@@ -3934,7 +3941,7 @@
         <v>46072</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -3945,7 +3952,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B45" s="8">
         <v>46077.51186719908</v>
@@ -3957,16 +3964,16 @@
         <v>46181.663148680556</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="8">
         <v>46073</v>
@@ -3984,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q45" s="8">
         <v>46073</v>
@@ -4010,7 +4017,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B46" s="5">
         <v>46077.51192424769</v>
@@ -4022,7 +4029,7 @@
         <v>46181.58443959491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4046,7 +4053,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4059,7 +4066,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B47" s="8">
         <v>46077.511929189815</v>
@@ -4071,16 +4078,16 @@
         <v>46181.66326342593</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I47" s="8">
         <v>46049</v>
@@ -4098,13 +4105,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q47" s="8">
         <v>46048</v>
@@ -4124,7 +4131,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B48" s="5">
         <v>46077.51193605324</v>
@@ -4136,16 +4143,16 @@
         <v>46181.663263993054</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I48" s="5">
         <v>46031</v>
@@ -4163,13 +4170,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48" s="5">
         <v>46031</v>
@@ -4189,7 +4196,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B49" s="8">
         <v>46077.51194265047</v>
@@ -4201,16 +4208,16 @@
         <v>46181.66326457176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I49" s="8">
         <v>46065</v>
@@ -4228,13 +4235,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49" s="8">
         <v>46065</v>
@@ -4254,7 +4261,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" s="5">
         <v>46077.511954409725</v>
@@ -4266,7 +4273,7 @@
         <v>46181.58580350694</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4290,7 +4297,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4303,7 +4310,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B51" s="8">
         <v>46077.51195832176</v>
@@ -4312,18 +4319,20 @@
         <v>46181.58428013889</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.663497326386</v>
+        <v>46223.8191834375</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="I51" s="8">
         <v>46076</v>
       </c>
@@ -4340,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51" s="8">
         <v>46076</v>
@@ -4366,7 +4375,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B52" s="5">
         <v>46077.511964687495</v>
@@ -4375,18 +4384,20 @@
         <v>46181.584470057875</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.663497939815</v>
+        <v>46223.81917953704</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="I52" s="5">
         <v>46083</v>
       </c>
@@ -4403,13 +4414,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4429,7 +4440,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B53" s="8">
         <v>46077.511973553235</v>
@@ -4438,18 +4449,20 @@
         <v>46181.5844784838</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.66349850694</v>
+        <v>46223.819175983794</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
         <v>46084</v>
@@ -4464,13 +4477,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q53" s="8">
         <v>46084</v>
@@ -4490,7 +4503,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="5">
         <v>46077.51198193287</v>
@@ -4499,18 +4512,20 @@
         <v>46181.5844847338</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.66349910879</v>
+        <v>46223.81917170139</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
         <v>46085</v>
@@ -4525,13 +4540,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4551,7 +4566,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B55" s="8">
         <v>46077.51201255787</v>
@@ -4560,18 +4575,20 @@
         <v>46181.58491251158</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.663499699076</v>
+        <v>46223.819168194445</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
         <v>46086</v>
@@ -4586,13 +4603,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4612,7 +4629,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B56" s="5">
         <v>46077.512021215276</v>
@@ -4621,18 +4638,20 @@
         <v>46181.58484026621</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.66350026621</v>
+        <v>46223.81916162037</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="I56" s="5">
         <v>46090</v>
       </c>
@@ -4649,13 +4668,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56" s="5">
         <v>46090</v>
@@ -4675,7 +4694,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B57" s="8">
         <v>46077.51202702546</v>
@@ -4687,7 +4706,7 @@
         <v>46181.58575875</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4711,7 +4730,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4724,7 +4743,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B58" s="5">
         <v>46077.51207347222</v>
@@ -4736,7 +4755,7 @@
         <v>46181.66365998842</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4757,19 +4776,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q58" s="5">
         <v>46091</v>
@@ -4789,7 +4808,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B59" s="8">
         <v>46077.51208324074</v>
@@ -4798,18 +4817,20 @@
         <v>46181.585011284726</v>
       </c>
       <c r="D59" s="8">
-        <v>46181.663658888894</v>
+        <v>46223.81920950231</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="I59" s="8">
         <v>46092</v>
       </c>
@@ -4826,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q59" s="8">
         <v>46092</v>
@@ -4852,7 +4873,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B60" s="5">
         <v>46077.5120906713</v>
@@ -4864,16 +4885,16 @@
         <v>46181.663659432874</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I60" s="5">
         <v>46093</v>
@@ -4891,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q60" s="5">
         <v>46093</v>
@@ -4917,7 +4938,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B61" s="8">
         <v>46077.512098148145</v>
@@ -4929,16 +4950,16 @@
         <v>46181.663660543985</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I61" s="8">
         <v>46094</v>
@@ -4956,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q61" s="8">
         <v>46094</v>
@@ -4982,7 +5003,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B62" s="5">
         <v>46077.512106423615</v>
@@ -4992,7 +5013,7 @@
         <v>46092.533237129624</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5016,7 +5037,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5029,7 +5050,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B63" s="8">
         <v>46077.512111296295</v>
@@ -5039,16 +5060,16 @@
         <v>46181.58500383102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I63" s="8">
         <v>46097</v>
@@ -5066,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q63" s="8">
         <v>46085</v>
@@ -5087,12 +5108,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B64" s="5">
         <v>46077.51211840278</v>
@@ -5102,16 +5123,16 @@
         <v>46182.59499232639</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I64" s="5">
         <v>46097</v>
@@ -5129,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q64" s="5">
         <v>46085</v>
@@ -5150,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="246">
   <si>
     <t xml:space="preserve"> 50001504 - ZITRON PERU CODESTABLE</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2318,7 +2321,7 @@
         <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18" s="5">
         <v>46022</v>
@@ -2330,7 +2333,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>26</v>
@@ -2342,7 +2345,7 @@
         <v>57</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46022</v>
@@ -2362,7 +2365,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="8">
         <v>46077.511631180554</v>
@@ -2374,7 +2377,7 @@
         <v>46223.81906576389</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2383,7 +2386,7 @@
         <v>80</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I19" s="8">
         <v>46024</v>
@@ -2395,7 +2398,7 @@
         <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>26</v>
@@ -2407,7 +2410,7 @@
         <v>61</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="8">
         <v>46024</v>
@@ -2427,7 +2430,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
         <v>46077.511489247685</v>
@@ -2439,7 +2442,7 @@
         <v>46181.58434696759</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2463,7 +2466,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2476,7 +2479,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" s="8">
         <v>46077.511642847225</v>
@@ -2488,16 +2491,16 @@
         <v>46104.59185236111</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" s="8">
         <v>46027</v>
@@ -2509,19 +2512,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="8">
         <v>46027</v>
@@ -2541,7 +2544,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B22" s="5">
         <v>46077.51164822916</v>
@@ -2553,16 +2556,16 @@
         <v>46104.59147082176</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I22" s="5">
         <v>46027</v>
@@ -2580,29 +2583,29 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="8">
         <v>46077.51165403935</v>
@@ -2614,16 +2617,16 @@
         <v>46104.59182434028</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="8">
         <v>46029</v>
@@ -2641,29 +2644,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5">
         <v>46077.51165996528</v>
@@ -2675,16 +2678,16 @@
         <v>46104.593614618054</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46027</v>
@@ -2702,13 +2705,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q24" s="5">
         <v>46027</v>
@@ -2728,7 +2731,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46077.51166581019</v>
@@ -2740,16 +2743,16 @@
         <v>46104.59354552084</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I25" s="8">
         <v>46027</v>
@@ -2767,29 +2770,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46077.51167158565</v>
@@ -2801,16 +2804,16 @@
         <v>46104.59358693287</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46029</v>
@@ -2828,29 +2831,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46077.5116772801</v>
@@ -2862,16 +2865,16 @@
         <v>46181.6626696875</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" s="8">
         <v>46027</v>
@@ -2883,19 +2886,19 @@
         <v>26</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q27" s="8">
         <v>46027</v>
@@ -2915,7 +2918,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
         <v>46077.51173550926</v>
@@ -2927,16 +2930,16 @@
         <v>46104.59468819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -2954,29 +2957,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" s="8">
         <v>46077.51174407407</v>
@@ -2988,16 +2991,16 @@
         <v>46174.619306099536</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I29" s="8">
         <v>46036</v>
@@ -3015,29 +3018,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46077.511750624995</v>
@@ -3049,16 +3052,16 @@
         <v>46127.7843647338</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46036</v>
@@ -3076,29 +3079,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="8">
         <v>46077.511757326385</v>
@@ -3110,16 +3113,16 @@
         <v>46104.593021875</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I31" s="8">
         <v>46028</v>
@@ -3137,13 +3140,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q31" s="8">
         <v>46028</v>
@@ -3163,7 +3166,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B32" s="5">
         <v>46077.51176472222</v>
@@ -3175,16 +3178,16 @@
         <v>46097.53370961806</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I32" s="5">
         <v>46028</v>
@@ -3202,29 +3205,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B33" s="8">
         <v>46077.511778726854</v>
@@ -3236,16 +3239,16 @@
         <v>46104.59299259259</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46037</v>
@@ -3263,29 +3266,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" s="5">
         <v>46077.511493680555</v>
@@ -3297,7 +3300,7 @@
         <v>46181.66279681713</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3321,7 +3324,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3334,7 +3337,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8">
         <v>46077.511804884256</v>
@@ -3346,16 +3349,16 @@
         <v>46098.51831884259</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I35" s="8">
         <v>46024</v>
@@ -3373,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>61</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q35" s="8">
         <v>46024</v>
@@ -3399,7 +3402,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B36" s="5">
         <v>46077.511813819445</v>
@@ -3411,16 +3414,16 @@
         <v>46132.59999503472</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I36" s="5">
         <v>46045</v>
@@ -3438,13 +3441,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q36" s="5">
         <v>46045</v>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B37" s="8">
         <v>46092.51508778935</v>
@@ -3476,16 +3479,16 @@
         <v>46132.60003634259</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3503,13 +3506,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q37" s="8">
         <v>46052</v>
@@ -3529,7 +3532,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B38" s="5">
         <v>46092.51515344907</v>
@@ -3541,16 +3544,16 @@
         <v>46181.66283061342</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I38" s="5">
         <v>46087</v>
@@ -3568,13 +3571,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q38" s="5">
         <v>46087</v>
@@ -3594,7 +3597,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B39" s="8">
         <v>46077.511823125</v>
@@ -3606,7 +3609,7 @@
         <v>46181.58436929398</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>25</v>
@@ -3630,7 +3633,7 @@
         <v>26</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3643,7 +3646,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B40" s="5">
         <v>46077.51182792824</v>
@@ -3655,16 +3658,16 @@
         <v>46181.66295334491</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I40" s="5">
         <v>46057</v>
@@ -3682,13 +3685,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q40" s="5">
         <v>46057</v>
@@ -3708,7 +3711,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B41" s="8">
         <v>46077.511842673615</v>
@@ -3720,16 +3723,16 @@
         <v>46181.66295386574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I41" s="8">
         <v>46059</v>
@@ -3747,13 +3750,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q41" s="8">
         <v>46059</v>
@@ -3773,7 +3776,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B42" s="5">
         <v>46077.51184961805</v>
@@ -3785,7 +3788,7 @@
         <v>46181.58441388889</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3809,7 +3812,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3822,7 +3825,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B43" s="8">
         <v>46077.511853495365</v>
@@ -3834,16 +3837,16 @@
         <v>46147.53564614583</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I43" s="8">
         <v>46063</v>
@@ -3861,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q43" s="8">
         <v>46063</v>
@@ -3887,7 +3890,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B44" s="5">
         <v>46077.51185981481</v>
@@ -3899,16 +3902,16 @@
         <v>46181.66309797454</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I44" s="5">
         <v>46066</v>
@@ -3926,13 +3929,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q44" s="5">
         <v>46066</v>
@@ -3941,7 +3944,7 @@
         <v>46072</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -3952,7 +3955,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B45" s="8">
         <v>46077.51186719908</v>
@@ -3964,16 +3967,16 @@
         <v>46181.663148680556</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I45" s="8">
         <v>46073</v>
@@ -3991,13 +3994,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q45" s="8">
         <v>46073</v>
@@ -4017,7 +4020,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B46" s="5">
         <v>46077.51192424769</v>
@@ -4029,7 +4032,7 @@
         <v>46181.58443959491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4053,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4066,7 +4069,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B47" s="8">
         <v>46077.511929189815</v>
@@ -4078,16 +4081,16 @@
         <v>46181.66326342593</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46049</v>
@@ -4105,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47" s="8">
         <v>46048</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B48" s="5">
         <v>46077.51193605324</v>
@@ -4143,16 +4146,16 @@
         <v>46181.663263993054</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46031</v>
@@ -4170,13 +4173,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48" s="5">
         <v>46031</v>
@@ -4196,7 +4199,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B49" s="8">
         <v>46077.51194265047</v>
@@ -4208,16 +4211,16 @@
         <v>46181.66326457176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46065</v>
@@ -4235,13 +4238,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q49" s="8">
         <v>46065</v>
@@ -4261,7 +4264,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B50" s="5">
         <v>46077.511954409725</v>
@@ -4273,7 +4276,7 @@
         <v>46181.58580350694</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4297,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4310,7 +4313,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B51" s="8">
         <v>46077.51195832176</v>
@@ -4322,7 +4325,7 @@
         <v>46223.8191834375</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4331,7 +4334,7 @@
         <v>80</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I51" s="8">
         <v>46076</v>
@@ -4349,13 +4352,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q51" s="8">
         <v>46076</v>
@@ -4375,7 +4378,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B52" s="5">
         <v>46077.511964687495</v>
@@ -4387,7 +4390,7 @@
         <v>46223.81917953704</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4396,7 +4399,7 @@
         <v>80</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I52" s="5">
         <v>46083</v>
@@ -4414,13 +4417,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4440,7 +4443,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B53" s="8">
         <v>46077.511973553235</v>
@@ -4452,7 +4455,7 @@
         <v>46223.819175983794</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -4461,7 +4464,7 @@
         <v>80</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4477,13 +4480,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q53" s="8">
         <v>46084</v>
@@ -4503,7 +4506,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B54" s="5">
         <v>46077.51198193287</v>
@@ -4515,7 +4518,7 @@
         <v>46223.81917170139</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4524,7 +4527,7 @@
         <v>80</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4540,13 +4543,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4566,7 +4569,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B55" s="8">
         <v>46077.51201255787</v>
@@ -4578,7 +4581,7 @@
         <v>46223.819168194445</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -4587,7 +4590,7 @@
         <v>80</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4603,13 +4606,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4629,7 +4632,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B56" s="5">
         <v>46077.512021215276</v>
@@ -4641,7 +4644,7 @@
         <v>46223.81916162037</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4650,7 +4653,7 @@
         <v>80</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I56" s="5">
         <v>46090</v>
@@ -4668,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56" s="5">
         <v>46090</v>
@@ -4694,7 +4697,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B57" s="8">
         <v>46077.51202702546</v>
@@ -4706,7 +4709,7 @@
         <v>46181.58575875</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4730,7 +4733,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4743,7 +4746,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B58" s="5">
         <v>46077.51207347222</v>
@@ -4755,7 +4758,7 @@
         <v>46181.66365998842</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4776,19 +4779,19 @@
         <v>26</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q58" s="5">
         <v>46091</v>
@@ -4808,7 +4811,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B59" s="8">
         <v>46077.51208324074</v>
@@ -4820,7 +4823,7 @@
         <v>46223.81920950231</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4829,7 +4832,7 @@
         <v>80</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I59" s="8">
         <v>46092</v>
@@ -4847,13 +4850,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q59" s="8">
         <v>46092</v>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B60" s="5">
         <v>46077.5120906713</v>
@@ -4885,16 +4888,16 @@
         <v>46181.663659432874</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I60" s="5">
         <v>46093</v>
@@ -4912,13 +4915,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q60" s="5">
         <v>46093</v>
@@ -4938,7 +4941,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B61" s="8">
         <v>46077.512098148145</v>
@@ -4950,16 +4953,16 @@
         <v>46181.663660543985</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I61" s="8">
         <v>46094</v>
@@ -4977,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61" s="8">
         <v>46094</v>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B62" s="5">
         <v>46077.512106423615</v>
@@ -5013,7 +5016,7 @@
         <v>46092.533237129624</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5037,7 +5040,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5050,7 +5053,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B63" s="8">
         <v>46077.512111296295</v>
@@ -5060,16 +5063,16 @@
         <v>46181.58500383102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I63" s="8">
         <v>46097</v>
@@ -5087,13 +5090,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q63" s="8">
         <v>46085</v>
@@ -5108,12 +5111,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B64" s="5">
         <v>46077.51211840278</v>
@@ -5123,16 +5126,16 @@
         <v>46182.59499232639</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I64" s="5">
         <v>46097</v>
@@ -5150,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q64" s="5">
         <v>46085</v>
@@ -5171,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -1618,7 +1618,7 @@
         <v>46092.723713935186</v>
       </c>
       <c r="D7" s="8">
-        <v>46100.637906805554</v>
+        <v>46226.564140381946</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -2439,7 +2439,7 @@
         <v>46181.58434533565</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.58434696759</v>
+        <v>46228.464923321764</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -3785,7 +3785,7 @@
         <v>46181.5844128125</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.58441388889</v>
+        <v>46228.228668194446</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>173</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -5011,9 +5011,11 @@
       <c r="B62" s="5">
         <v>46077.512106423615</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46240.60840010417</v>
+      </c>
       <c r="D62" s="5">
-        <v>46092.533237129624</v>
+        <v>46240.60840165509</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>237</v>
@@ -5058,9 +5060,11 @@
       <c r="B63" s="8">
         <v>46077.512111296295</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46240.607980057874</v>
+      </c>
       <c r="D63" s="8">
-        <v>46181.58500383102</v>
+        <v>46240.60846284722</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5108,10 +5112,10 @@
         <v>32</v>
       </c>
       <c r="T63" s="9">
-        <v>0</v>
-      </c>
-      <c r="U63" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U63" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5121,9 +5125,11 @@
       <c r="B64" s="5">
         <v>46077.51211840278</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46240.60799158565</v>
+      </c>
       <c r="D64" s="5">
-        <v>46182.59499232639</v>
+        <v>46240.608487488425</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>244</v>
@@ -5171,10 +5177,10 @@
         <v>32</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -1431,13 +1431,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.51147570602</v>
+        <v>46077.34480903935</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72374829861</v>
+        <v>46092.557081631945</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.784329155096</v>
+        <v>46118.617662488425</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1482,13 +1482,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.51154885416</v>
+        <v>46077.3448821875</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.723712962965</v>
+        <v>46092.55704629629</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.901517754624</v>
+        <v>46133.73485108797</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1547,13 +1547,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.511553495366</v>
+        <v>46077.34488682871</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.723713495376</v>
+        <v>46092.557046828704</v>
       </c>
       <c r="D6" s="5">
-        <v>46100.64636372685</v>
+        <v>46100.47969706019</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1612,13 +1612,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.511557418984</v>
+        <v>46077.34489075231</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.723713935186</v>
+        <v>46092.55704726852</v>
       </c>
       <c r="D7" s="8">
-        <v>46226.564140381946</v>
+        <v>46226.397473715275</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
@@ -1677,13 +1677,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.51156111111</v>
+        <v>46077.344894444446</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.7237144213</v>
+        <v>46092.55704775463</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.69251282407</v>
+        <v>46100.52584615741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1742,13 +1742,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.51156568287</v>
+        <v>46077.3448990162</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.723715127315</v>
+        <v>46092.55704846064</v>
       </c>
       <c r="D9" s="8">
-        <v>46100.67660435185</v>
+        <v>46100.50993768519</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
@@ -1807,13 +1807,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.511480243054</v>
+        <v>46077.34481357639</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.52695974537</v>
+        <v>46114.3602930787</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.52697136574</v>
+        <v>46114.360304699076</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -1860,13 +1860,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.51157018519</v>
+        <v>46077.34490351852</v>
       </c>
       <c r="C11" s="8">
-        <v>46100.64395409722</v>
+        <v>46100.477287430556</v>
       </c>
       <c r="D11" s="8">
-        <v>46100.643973819446</v>
+        <v>46100.477307152774</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -1925,13 +1925,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.5115900463</v>
+        <v>46077.34492337963</v>
       </c>
       <c r="C12" s="5">
-        <v>46100.644285208335</v>
+        <v>46100.47761854167</v>
       </c>
       <c r="D12" s="5">
-        <v>46100.690858877315</v>
+        <v>46100.52419221065</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -1990,13 +1990,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46077.511595937496</v>
+        <v>46077.34492927083</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.53360980324</v>
+        <v>46097.36694313657</v>
       </c>
       <c r="D13" s="8">
-        <v>46101.819566875</v>
+        <v>46101.65290020833</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2055,13 +2055,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46077.51160226852</v>
+        <v>46077.344935601854</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.5269425</v>
+        <v>46114.36027583333</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.526961006944</v>
+        <v>46114.36029434028</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2120,13 +2120,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="8">
-        <v>46077.51148475695</v>
+        <v>46077.34481809028</v>
       </c>
       <c r="C15" s="8">
-        <v>46100.65183821759</v>
+        <v>46100.48517155093</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.6518556713</v>
+        <v>46100.48518900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2173,13 +2173,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46077.51161194444</v>
+        <v>46077.34494527778</v>
       </c>
       <c r="C16" s="5">
-        <v>46100.6514</v>
+        <v>46100.48473333333</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.66261890046</v>
+        <v>46181.495952233796</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2238,13 +2238,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.511618379634</v>
+        <v>46077.34495171296</v>
       </c>
       <c r="C17" s="8">
-        <v>46100.65097256945</v>
+        <v>46100.48430590278</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.65176030093</v>
+        <v>46100.485093634255</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2303,13 +2303,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.511624872684</v>
+        <v>46077.34495820602</v>
       </c>
       <c r="C18" s="5">
-        <v>46100.651822280095</v>
+        <v>46100.48515561342</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.81906920139</v>
+        <v>46223.65240253472</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2368,13 +2368,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.511631180554</v>
+        <v>46077.34496451389</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.53366215278</v>
+        <v>46097.36699548611</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.81906576389</v>
+        <v>46223.65239909722</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>85</v>
@@ -2433,13 +2433,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.511489247685</v>
+        <v>46077.34482258101</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.58434533565</v>
+        <v>46181.41767866898</v>
       </c>
       <c r="D20" s="5">
-        <v>46228.464923321764</v>
+        <v>46228.29825665509</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2482,13 +2482,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.511642847225</v>
+        <v>46077.34497618055</v>
       </c>
       <c r="C21" s="8">
-        <v>46104.59183936343</v>
+        <v>46104.42517269676</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.59185236111</v>
+        <v>46104.42518569445</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>92</v>
@@ -2547,13 +2547,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.51164822916</v>
+        <v>46077.3449815625</v>
       </c>
       <c r="C22" s="5">
-        <v>46104.59146888889</v>
+        <v>46104.424802222224</v>
       </c>
       <c r="D22" s="5">
-        <v>46104.59147082176</v>
+        <v>46104.42480415509</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2608,13 +2608,13 @@
         <v>102</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.51165403935</v>
+        <v>46077.344987372686</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.59182263889</v>
+        <v>46104.42515597222</v>
       </c>
       <c r="D23" s="8">
-        <v>46104.59182434028</v>
+        <v>46104.42515767361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>103</v>
@@ -2669,13 +2669,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.51165996528</v>
+        <v>46077.34499329861</v>
       </c>
       <c r="C24" s="5">
-        <v>46104.59360127315</v>
+        <v>46104.42693460648</v>
       </c>
       <c r="D24" s="5">
-        <v>46104.593614618054</v>
+        <v>46104.42694795139</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>106</v>
@@ -2734,13 +2734,13 @@
         <v>108</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.51166581019</v>
+        <v>46077.34499914352</v>
       </c>
       <c r="C25" s="8">
-        <v>46104.59354353009</v>
+        <v>46104.42687686342</v>
       </c>
       <c r="D25" s="8">
-        <v>46104.59354552084</v>
+        <v>46104.42687885417</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>109</v>
@@ -2795,13 +2795,13 @@
         <v>111</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.51167158565</v>
+        <v>46077.345004918985</v>
       </c>
       <c r="C26" s="5">
-        <v>46104.59358512731</v>
+        <v>46104.42691846065</v>
       </c>
       <c r="D26" s="5">
-        <v>46104.59358693287</v>
+        <v>46104.4269202662</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>112</v>
@@ -2856,13 +2856,13 @@
         <v>114</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.5116772801</v>
+        <v>46077.345010613426</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.61983740741</v>
+        <v>46174.453170740744</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.6626696875</v>
+        <v>46181.49600302083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>115</v>
@@ -2921,13 +2921,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.51173550926</v>
+        <v>46077.345068842595</v>
       </c>
       <c r="C28" s="5">
-        <v>46104.5946865625</v>
+        <v>46104.42801989583</v>
       </c>
       <c r="D28" s="5">
-        <v>46104.59468819444</v>
+        <v>46104.42802152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -2982,13 +2982,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.51174407407</v>
+        <v>46077.34507740741</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.61930413195</v>
+        <v>46174.45263746528</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.619306099536</v>
+        <v>46174.45263943287</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3043,13 +3043,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46077.511750624995</v>
+        <v>46077.34508395834</v>
       </c>
       <c r="C30" s="5">
-        <v>46127.78436329861</v>
+        <v>46127.61769663195</v>
       </c>
       <c r="D30" s="5">
-        <v>46127.7843647338</v>
+        <v>46127.61769806713</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3104,13 +3104,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.511757326385</v>
+        <v>46077.34509065972</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.59300746528</v>
+        <v>46104.426340798615</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.593021875</v>
+        <v>46104.42635520833</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3169,13 +3169,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.51176472222</v>
+        <v>46077.34509805556</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53370762731</v>
+        <v>46097.36704096065</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.53370961806</v>
+        <v>46097.36704295139</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3230,13 +3230,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.511778726854</v>
+        <v>46077.34511206018</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.59299090278</v>
+        <v>46104.42632423611</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.59299259259</v>
+        <v>46104.426325925924</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3291,13 +3291,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.511493680555</v>
+        <v>46077.34482701389</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.58435664352</v>
+        <v>46181.41768997685</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.66279681713</v>
+        <v>46181.496130150466</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3340,13 +3340,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.511804884256</v>
+        <v>46077.34513821759</v>
       </c>
       <c r="C35" s="8">
-        <v>46098.5182991551</v>
+        <v>46098.351632488426</v>
       </c>
       <c r="D35" s="8">
-        <v>46098.51831884259</v>
+        <v>46098.35165217593</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3405,13 +3405,13 @@
         <v>146</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.511813819445</v>
+        <v>46077.34514715278</v>
       </c>
       <c r="C36" s="5">
-        <v>46132.59997896991</v>
+        <v>46132.43331230324</v>
       </c>
       <c r="D36" s="5">
-        <v>46132.59999503472</v>
+        <v>46132.43332836806</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>147</v>
@@ -3470,13 +3470,13 @@
         <v>150</v>
       </c>
       <c r="B37" s="8">
-        <v>46092.51508778935</v>
+        <v>46092.34842112269</v>
       </c>
       <c r="C37" s="8">
-        <v>46132.600021226855</v>
+        <v>46132.433354560184</v>
       </c>
       <c r="D37" s="8">
-        <v>46132.60003634259</v>
+        <v>46132.43336967593</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>151</v>
@@ -3535,13 +3535,13 @@
         <v>153</v>
       </c>
       <c r="B38" s="5">
-        <v>46092.51515344907</v>
+        <v>46092.34848678241</v>
       </c>
       <c r="C38" s="5">
-        <v>46181.584749965274</v>
+        <v>46181.41808329861</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.66283061342</v>
+        <v>46181.49616394676</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>154</v>
@@ -3600,13 +3600,13 @@
         <v>159</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.511823125</v>
+        <v>46077.34515645834</v>
       </c>
       <c r="C39" s="8">
-        <v>46181.584367777774</v>
+        <v>46181.41770111111</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.58436929398</v>
+        <v>46181.41770262731</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>160</v>
@@ -3649,13 +3649,13 @@
         <v>162</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.51182792824</v>
+        <v>46077.345161261575</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.58420413194</v>
+        <v>46181.41753746528</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.66295334491</v>
+        <v>46181.496286678244</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>163</v>
@@ -3714,13 +3714,13 @@
         <v>167</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.511842673615</v>
+        <v>46077.345176006944</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.535636643515</v>
+        <v>46147.36896997685</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.66295386574</v>
+        <v>46181.49628719907</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>168</v>
@@ -3779,13 +3779,13 @@
         <v>172</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.51184961805</v>
+        <v>46077.345182951394</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.5844128125</v>
+        <v>46181.41774614583</v>
       </c>
       <c r="D42" s="5">
-        <v>46228.228668194446</v>
+        <v>46228.06200152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>173</v>
@@ -3828,13 +3828,13 @@
         <v>175</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.511853495365</v>
+        <v>46077.34518682871</v>
       </c>
       <c r="C43" s="8">
-        <v>46128.502038506944</v>
+        <v>46128.33537184028</v>
       </c>
       <c r="D43" s="8">
-        <v>46147.53564614583</v>
+        <v>46147.36897947917</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>176</v>
@@ -3893,13 +3893,13 @@
         <v>180</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.51185981481</v>
+        <v>46077.34519314815</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.591328703704</v>
+        <v>46146.42466203704</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66309797454</v>
+        <v>46181.49643130787</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>181</v>
@@ -3958,13 +3958,13 @@
         <v>184</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.51186719908</v>
+        <v>46077.34520053241</v>
       </c>
       <c r="C45" s="8">
-        <v>46147.535923564814</v>
+        <v>46147.36925689815</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.663148680556</v>
+        <v>46181.496482013885</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>185</v>
@@ -4023,13 +4023,13 @@
         <v>188</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.51192424769</v>
+        <v>46077.34525758102</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.58443833333</v>
+        <v>46181.41777166667</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.58443959491</v>
+        <v>46181.41777292824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -4072,13 +4072,13 @@
         <v>190</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.511929189815</v>
+        <v>46077.345262523144</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.58425488426</v>
+        <v>46181.41758821759</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66326342593</v>
+        <v>46181.49659675926</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>191</v>
@@ -4137,13 +4137,13 @@
         <v>193</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.51193605324</v>
+        <v>46077.34526938657</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.58426366898</v>
+        <v>46181.41759700231</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.663263993054</v>
+        <v>46181.49659732639</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>194</v>
@@ -4202,13 +4202,13 @@
         <v>196</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.51194265047</v>
+        <v>46077.3452759838</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.58426854167</v>
+        <v>46181.417601875</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66326457176</v>
+        <v>46181.49659790509</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>197</v>
@@ -4267,13 +4267,13 @@
         <v>199</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.511954409725</v>
+        <v>46077.34528774305</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.5858024537</v>
+        <v>46181.41913578704</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.58580350694</v>
+        <v>46181.41913684028</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>200</v>
@@ -4316,13 +4316,13 @@
         <v>202</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.51195832176</v>
+        <v>46077.34529165509</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.58428013889</v>
+        <v>46181.41761347222</v>
       </c>
       <c r="D51" s="8">
-        <v>46223.8191834375</v>
+        <v>46223.65251677083</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>203</v>
@@ -4381,13 +4381,13 @@
         <v>205</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.511964687495</v>
+        <v>46077.34529802084</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.584470057875</v>
+        <v>46181.4178033912</v>
       </c>
       <c r="D52" s="5">
-        <v>46223.81917953704</v>
+        <v>46223.652512870365</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>206</v>
@@ -4446,13 +4446,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.511973553235</v>
+        <v>46077.34530688658</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.5844784838</v>
+        <v>46181.417811817126</v>
       </c>
       <c r="D53" s="8">
-        <v>46223.819175983794</v>
+        <v>46223.65250931713</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4509,13 +4509,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.51198193287</v>
+        <v>46077.345315266204</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.5844847338</v>
+        <v>46181.41781806713</v>
       </c>
       <c r="D54" s="5">
-        <v>46223.81917170139</v>
+        <v>46223.652505034726</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4572,13 +4572,13 @@
         <v>215</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.51201255787</v>
+        <v>46077.345345891204</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.58491251158</v>
+        <v>46181.41824584491</v>
       </c>
       <c r="D55" s="8">
-        <v>46223.819168194445</v>
+        <v>46223.65250152777</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>157</v>
@@ -4635,13 +4635,13 @@
         <v>218</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.512021215276</v>
+        <v>46077.34535454861</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.58484026621</v>
+        <v>46181.41817359954</v>
       </c>
       <c r="D56" s="5">
-        <v>46223.81916162037</v>
+        <v>46223.652494953705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>158</v>
@@ -4700,13 +4700,13 @@
         <v>220</v>
       </c>
       <c r="B57" s="8">
-        <v>46077.51202702546</v>
+        <v>46077.3453603588</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.58575745371</v>
+        <v>46181.419090787036</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.58575875</v>
+        <v>46181.419092083335</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>221</v>
@@ -4749,13 +4749,13 @@
         <v>223</v>
       </c>
       <c r="B58" s="5">
-        <v>46077.51207347222</v>
+        <v>46077.34540680556</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.584975081016</v>
+        <v>46181.41830841435</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.66365998842</v>
+        <v>46181.49699332176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>224</v>
@@ -4814,13 +4814,13 @@
         <v>227</v>
       </c>
       <c r="B59" s="8">
-        <v>46077.51208324074</v>
+        <v>46077.34541657407</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.585011284726</v>
+        <v>46181.418344618054</v>
       </c>
       <c r="D59" s="8">
-        <v>46223.81920950231</v>
+        <v>46223.65254283565</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>228</v>
@@ -4879,13 +4879,13 @@
         <v>230</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.5120906713</v>
+        <v>46077.34542400463</v>
       </c>
       <c r="C60" s="5">
-        <v>46150.695240960646</v>
+        <v>46150.52857429398</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.663659432874</v>
+        <v>46181.4969927662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>231</v>
@@ -4944,13 +4944,13 @@
         <v>233</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.512098148145</v>
+        <v>46077.34543148148</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.58499498843</v>
+        <v>46181.41832832176</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.663660543985</v>
+        <v>46181.496993877314</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>234</v>
@@ -5009,13 +5009,13 @@
         <v>236</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.512106423615</v>
+        <v>46077.345439756944</v>
       </c>
       <c r="C62" s="5">
-        <v>46240.60840010417</v>
+        <v>46240.4417334375</v>
       </c>
       <c r="D62" s="5">
-        <v>46240.60840165509</v>
+        <v>46240.441734988424</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>237</v>
@@ -5058,13 +5058,13 @@
         <v>239</v>
       </c>
       <c r="B63" s="8">
-        <v>46077.512111296295</v>
+        <v>46077.34544462963</v>
       </c>
       <c r="C63" s="8">
-        <v>46240.607980057874</v>
+        <v>46240.4413133912</v>
       </c>
       <c r="D63" s="8">
-        <v>46240.60846284722</v>
+        <v>46240.44179618056</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5123,13 +5123,13 @@
         <v>243</v>
       </c>
       <c r="B64" s="5">
-        <v>46077.51211840278</v>
+        <v>46077.34545173611</v>
       </c>
       <c r="C64" s="5">
-        <v>46240.60799158565</v>
+        <v>46240.44132491898</v>
       </c>
       <c r="D64" s="5">
-        <v>46240.608487488425</v>
+        <v>46240.441820821754</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>244</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -1431,13 +1431,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.34480903935</v>
+        <v>46077.51147570602</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557081631945</v>
+        <v>46092.72374829861</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.617662488425</v>
+        <v>46118.784329155096</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1482,13 +1482,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.3448821875</v>
+        <v>46077.51154885416</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55704629629</v>
+        <v>46092.723712962965</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.73485108797</v>
+        <v>46133.901517754624</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1547,13 +1547,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.34488682871</v>
+        <v>46077.511553495366</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557046828704</v>
+        <v>46092.723713495376</v>
       </c>
       <c r="D6" s="5">
-        <v>46100.47969706019</v>
+        <v>46100.64636372685</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1612,13 +1612,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.34489075231</v>
+        <v>46077.511557418984</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55704726852</v>
+        <v>46092.723713935186</v>
       </c>
       <c r="D7" s="8">
-        <v>46226.397473715275</v>
+        <v>46226.564140381946</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>40</v>
@@ -1677,13 +1677,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.344894444446</v>
+        <v>46077.51156111111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55704775463</v>
+        <v>46092.7237144213</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.52584615741</v>
+        <v>46100.69251282407</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>43</v>
@@ -1742,13 +1742,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.3448990162</v>
+        <v>46077.51156568287</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55704846064</v>
+        <v>46092.723715127315</v>
       </c>
       <c r="D9" s="8">
-        <v>46100.50993768519</v>
+        <v>46100.67660435185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
@@ -1807,13 +1807,13 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.34481357639</v>
+        <v>46077.511480243054</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.3602930787</v>
+        <v>46114.52695974537</v>
       </c>
       <c r="D10" s="5">
-        <v>46114.360304699076</v>
+        <v>46114.52697136574</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -1860,13 +1860,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.34490351852</v>
+        <v>46077.51157018519</v>
       </c>
       <c r="C11" s="8">
-        <v>46100.477287430556</v>
+        <v>46100.64395409722</v>
       </c>
       <c r="D11" s="8">
-        <v>46100.477307152774</v>
+        <v>46100.643973819446</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -1925,13 +1925,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.34492337963</v>
+        <v>46077.5115900463</v>
       </c>
       <c r="C12" s="5">
-        <v>46100.47761854167</v>
+        <v>46100.644285208335</v>
       </c>
       <c r="D12" s="5">
-        <v>46100.52419221065</v>
+        <v>46100.690858877315</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -1990,13 +1990,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46077.34492927083</v>
+        <v>46077.511595937496</v>
       </c>
       <c r="C13" s="8">
-        <v>46097.36694313657</v>
+        <v>46097.53360980324</v>
       </c>
       <c r="D13" s="8">
-        <v>46101.65290020833</v>
+        <v>46101.819566875</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2055,13 +2055,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46077.344935601854</v>
+        <v>46077.51160226852</v>
       </c>
       <c r="C14" s="5">
-        <v>46114.36027583333</v>
+        <v>46114.5269425</v>
       </c>
       <c r="D14" s="5">
-        <v>46114.36029434028</v>
+        <v>46114.526961006944</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2120,13 +2120,13 @@
         <v>68</v>
       </c>
       <c r="B15" s="8">
-        <v>46077.34481809028</v>
+        <v>46077.51148475695</v>
       </c>
       <c r="C15" s="8">
-        <v>46100.48517155093</v>
+        <v>46100.65183821759</v>
       </c>
       <c r="D15" s="8">
-        <v>46100.48518900463</v>
+        <v>46100.6518556713</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>69</v>
@@ -2173,13 +2173,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46077.34494527778</v>
+        <v>46077.51161194444</v>
       </c>
       <c r="C16" s="5">
-        <v>46100.48473333333</v>
+        <v>46100.6514</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.495952233796</v>
+        <v>46181.66261890046</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2238,13 +2238,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.34495171296</v>
+        <v>46077.511618379634</v>
       </c>
       <c r="C17" s="8">
-        <v>46100.48430590278</v>
+        <v>46100.65097256945</v>
       </c>
       <c r="D17" s="8">
-        <v>46100.485093634255</v>
+        <v>46100.65176030093</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2303,13 +2303,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.34495820602</v>
+        <v>46077.511624872684</v>
       </c>
       <c r="C18" s="5">
-        <v>46100.48515561342</v>
+        <v>46100.651822280095</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.65240253472</v>
+        <v>46223.81906920139</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2368,13 +2368,13 @@
         <v>84</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.34496451389</v>
+        <v>46077.511631180554</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36699548611</v>
+        <v>46097.53366215278</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.65239909722</v>
+        <v>46223.81906576389</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>85</v>
@@ -2433,13 +2433,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.34482258101</v>
+        <v>46077.511489247685</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.41767866898</v>
+        <v>46181.58434533565</v>
       </c>
       <c r="D20" s="5">
-        <v>46228.29825665509</v>
+        <v>46228.464923321764</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2482,13 +2482,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.34497618055</v>
+        <v>46077.511642847225</v>
       </c>
       <c r="C21" s="8">
-        <v>46104.42517269676</v>
+        <v>46104.59183936343</v>
       </c>
       <c r="D21" s="8">
-        <v>46104.42518569445</v>
+        <v>46104.59185236111</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>92</v>
@@ -2547,13 +2547,13 @@
         <v>97</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.3449815625</v>
+        <v>46077.51164822916</v>
       </c>
       <c r="C22" s="5">
-        <v>46104.424802222224</v>
+        <v>46104.59146888889</v>
       </c>
       <c r="D22" s="5">
-        <v>46104.42480415509</v>
+        <v>46104.59147082176</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
@@ -2608,13 +2608,13 @@
         <v>102</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.344987372686</v>
+        <v>46077.51165403935</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.42515597222</v>
+        <v>46104.59182263889</v>
       </c>
       <c r="D23" s="8">
-        <v>46104.42515767361</v>
+        <v>46104.59182434028</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>103</v>
@@ -2669,13 +2669,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.34499329861</v>
+        <v>46077.51165996528</v>
       </c>
       <c r="C24" s="5">
-        <v>46104.42693460648</v>
+        <v>46104.59360127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46104.42694795139</v>
+        <v>46104.593614618054</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>106</v>
@@ -2734,13 +2734,13 @@
         <v>108</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.34499914352</v>
+        <v>46077.51166581019</v>
       </c>
       <c r="C25" s="8">
-        <v>46104.42687686342</v>
+        <v>46104.59354353009</v>
       </c>
       <c r="D25" s="8">
-        <v>46104.42687885417</v>
+        <v>46104.59354552084</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>109</v>
@@ -2795,13 +2795,13 @@
         <v>111</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.345004918985</v>
+        <v>46077.51167158565</v>
       </c>
       <c r="C26" s="5">
-        <v>46104.42691846065</v>
+        <v>46104.59358512731</v>
       </c>
       <c r="D26" s="5">
-        <v>46104.4269202662</v>
+        <v>46104.59358693287</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>112</v>
@@ -2856,13 +2856,13 @@
         <v>114</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.345010613426</v>
+        <v>46077.5116772801</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.453170740744</v>
+        <v>46174.61983740741</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.49600302083</v>
+        <v>46181.6626696875</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>115</v>
@@ -2921,13 +2921,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.345068842595</v>
+        <v>46077.51173550926</v>
       </c>
       <c r="C28" s="5">
-        <v>46104.42801989583</v>
+        <v>46104.5946865625</v>
       </c>
       <c r="D28" s="5">
-        <v>46104.42802152778</v>
+        <v>46104.59468819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -2982,13 +2982,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.34507740741</v>
+        <v>46077.51174407407</v>
       </c>
       <c r="C29" s="8">
-        <v>46174.45263746528</v>
+        <v>46174.61930413195</v>
       </c>
       <c r="D29" s="8">
-        <v>46174.45263943287</v>
+        <v>46174.619306099536</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3043,13 +3043,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46077.34508395834</v>
+        <v>46077.511750624995</v>
       </c>
       <c r="C30" s="5">
-        <v>46127.61769663195</v>
+        <v>46127.78436329861</v>
       </c>
       <c r="D30" s="5">
-        <v>46127.61769806713</v>
+        <v>46127.7843647338</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3104,13 +3104,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.34509065972</v>
+        <v>46077.511757326385</v>
       </c>
       <c r="C31" s="8">
-        <v>46104.426340798615</v>
+        <v>46104.59300746528</v>
       </c>
       <c r="D31" s="8">
-        <v>46104.42635520833</v>
+        <v>46104.593021875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3169,13 +3169,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.34509805556</v>
+        <v>46077.51176472222</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.36704096065</v>
+        <v>46097.53370762731</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.36704295139</v>
+        <v>46097.53370961806</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3230,13 +3230,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.34511206018</v>
+        <v>46077.511778726854</v>
       </c>
       <c r="C33" s="8">
-        <v>46104.42632423611</v>
+        <v>46104.59299090278</v>
       </c>
       <c r="D33" s="8">
-        <v>46104.426325925924</v>
+        <v>46104.59299259259</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3291,13 +3291,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.34482701389</v>
+        <v>46077.511493680555</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.41768997685</v>
+        <v>46181.58435664352</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.496130150466</v>
+        <v>46181.66279681713</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3340,13 +3340,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.34513821759</v>
+        <v>46077.511804884256</v>
       </c>
       <c r="C35" s="8">
-        <v>46098.351632488426</v>
+        <v>46098.5182991551</v>
       </c>
       <c r="D35" s="8">
-        <v>46098.35165217593</v>
+        <v>46098.51831884259</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3405,13 +3405,13 @@
         <v>146</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.34514715278</v>
+        <v>46077.511813819445</v>
       </c>
       <c r="C36" s="5">
-        <v>46132.43331230324</v>
+        <v>46132.59997896991</v>
       </c>
       <c r="D36" s="5">
-        <v>46132.43332836806</v>
+        <v>46132.59999503472</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>147</v>
@@ -3470,13 +3470,13 @@
         <v>150</v>
       </c>
       <c r="B37" s="8">
-        <v>46092.34842112269</v>
+        <v>46092.51508778935</v>
       </c>
       <c r="C37" s="8">
-        <v>46132.433354560184</v>
+        <v>46132.600021226855</v>
       </c>
       <c r="D37" s="8">
-        <v>46132.43336967593</v>
+        <v>46132.60003634259</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>151</v>
@@ -3535,13 +3535,13 @@
         <v>153</v>
       </c>
       <c r="B38" s="5">
-        <v>46092.34848678241</v>
+        <v>46092.51515344907</v>
       </c>
       <c r="C38" s="5">
-        <v>46181.41808329861</v>
+        <v>46181.584749965274</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.49616394676</v>
+        <v>46181.66283061342</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>154</v>
@@ -3600,13 +3600,13 @@
         <v>159</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.34515645834</v>
+        <v>46077.511823125</v>
       </c>
       <c r="C39" s="8">
-        <v>46181.41770111111</v>
+        <v>46181.584367777774</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.41770262731</v>
+        <v>46181.58436929398</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>160</v>
@@ -3649,13 +3649,13 @@
         <v>162</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.345161261575</v>
+        <v>46077.51182792824</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.41753746528</v>
+        <v>46181.58420413194</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.496286678244</v>
+        <v>46181.66295334491</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>163</v>
@@ -3714,13 +3714,13 @@
         <v>167</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.345176006944</v>
+        <v>46077.511842673615</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.36896997685</v>
+        <v>46147.535636643515</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.49628719907</v>
+        <v>46181.66295386574</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>168</v>
@@ -3779,13 +3779,13 @@
         <v>172</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.345182951394</v>
+        <v>46077.51184961805</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.41774614583</v>
+        <v>46181.5844128125</v>
       </c>
       <c r="D42" s="5">
-        <v>46228.06200152778</v>
+        <v>46228.228668194446</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>173</v>
@@ -3828,13 +3828,13 @@
         <v>175</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.34518682871</v>
+        <v>46077.511853495365</v>
       </c>
       <c r="C43" s="8">
-        <v>46128.33537184028</v>
+        <v>46128.502038506944</v>
       </c>
       <c r="D43" s="8">
-        <v>46147.36897947917</v>
+        <v>46147.53564614583</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>176</v>
@@ -3893,13 +3893,13 @@
         <v>180</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.34519314815</v>
+        <v>46077.51185981481</v>
       </c>
       <c r="C44" s="5">
-        <v>46146.42466203704</v>
+        <v>46146.591328703704</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.49643130787</v>
+        <v>46181.66309797454</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>181</v>
@@ -3958,13 +3958,13 @@
         <v>184</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.34520053241</v>
+        <v>46077.51186719908</v>
       </c>
       <c r="C45" s="8">
-        <v>46147.36925689815</v>
+        <v>46147.535923564814</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.496482013885</v>
+        <v>46181.663148680556</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>185</v>
@@ -4023,13 +4023,13 @@
         <v>188</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.34525758102</v>
+        <v>46077.51192424769</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.41777166667</v>
+        <v>46181.58443833333</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.41777292824</v>
+        <v>46181.58443959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -4072,13 +4072,13 @@
         <v>190</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.345262523144</v>
+        <v>46077.511929189815</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.41758821759</v>
+        <v>46181.58425488426</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.49659675926</v>
+        <v>46181.66326342593</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>191</v>
@@ -4137,13 +4137,13 @@
         <v>193</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.34526938657</v>
+        <v>46077.51193605324</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.41759700231</v>
+        <v>46181.58426366898</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.49659732639</v>
+        <v>46181.663263993054</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>194</v>
@@ -4202,13 +4202,13 @@
         <v>196</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.3452759838</v>
+        <v>46077.51194265047</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.417601875</v>
+        <v>46181.58426854167</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.49659790509</v>
+        <v>46181.66326457176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>197</v>
@@ -4267,13 +4267,13 @@
         <v>199</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.34528774305</v>
+        <v>46077.511954409725</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.41913578704</v>
+        <v>46181.5858024537</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.41913684028</v>
+        <v>46181.58580350694</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>200</v>
@@ -4316,13 +4316,13 @@
         <v>202</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.34529165509</v>
+        <v>46077.51195832176</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.41761347222</v>
+        <v>46181.58428013889</v>
       </c>
       <c r="D51" s="8">
-        <v>46223.65251677083</v>
+        <v>46223.8191834375</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>203</v>
@@ -4381,13 +4381,13 @@
         <v>205</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.34529802084</v>
+        <v>46077.511964687495</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.4178033912</v>
+        <v>46181.584470057875</v>
       </c>
       <c r="D52" s="5">
-        <v>46223.652512870365</v>
+        <v>46223.81917953704</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>206</v>
@@ -4446,13 +4446,13 @@
         <v>209</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.34530688658</v>
+        <v>46077.511973553235</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.417811817126</v>
+        <v>46181.5844784838</v>
       </c>
       <c r="D53" s="8">
-        <v>46223.65250931713</v>
+        <v>46223.819175983794</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>210</v>
@@ -4509,13 +4509,13 @@
         <v>212</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.345315266204</v>
+        <v>46077.51198193287</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.41781806713</v>
+        <v>46181.5844847338</v>
       </c>
       <c r="D54" s="5">
-        <v>46223.652505034726</v>
+        <v>46223.81917170139</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>213</v>
@@ -4572,13 +4572,13 @@
         <v>215</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.345345891204</v>
+        <v>46077.51201255787</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.41824584491</v>
+        <v>46181.58491251158</v>
       </c>
       <c r="D55" s="8">
-        <v>46223.65250152777</v>
+        <v>46223.819168194445</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>157</v>
@@ -4635,13 +4635,13 @@
         <v>218</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.34535454861</v>
+        <v>46077.512021215276</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.41817359954</v>
+        <v>46181.58484026621</v>
       </c>
       <c r="D56" s="5">
-        <v>46223.652494953705</v>
+        <v>46223.81916162037</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>158</v>
@@ -4700,13 +4700,13 @@
         <v>220</v>
       </c>
       <c r="B57" s="8">
-        <v>46077.3453603588</v>
+        <v>46077.51202702546</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.419090787036</v>
+        <v>46181.58575745371</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.419092083335</v>
+        <v>46181.58575875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>221</v>
@@ -4749,13 +4749,13 @@
         <v>223</v>
       </c>
       <c r="B58" s="5">
-        <v>46077.34540680556</v>
+        <v>46077.51207347222</v>
       </c>
       <c r="C58" s="5">
-        <v>46181.41830841435</v>
+        <v>46181.584975081016</v>
       </c>
       <c r="D58" s="5">
-        <v>46181.49699332176</v>
+        <v>46181.66365998842</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>224</v>
@@ -4814,13 +4814,13 @@
         <v>227</v>
       </c>
       <c r="B59" s="8">
-        <v>46077.34541657407</v>
+        <v>46077.51208324074</v>
       </c>
       <c r="C59" s="8">
-        <v>46181.418344618054</v>
+        <v>46181.585011284726</v>
       </c>
       <c r="D59" s="8">
-        <v>46223.65254283565</v>
+        <v>46223.81920950231</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>228</v>
@@ -4879,13 +4879,13 @@
         <v>230</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.34542400463</v>
+        <v>46077.5120906713</v>
       </c>
       <c r="C60" s="5">
-        <v>46150.52857429398</v>
+        <v>46150.695240960646</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.4969927662</v>
+        <v>46181.663659432874</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>231</v>
@@ -4944,13 +4944,13 @@
         <v>233</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.34543148148</v>
+        <v>46077.512098148145</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.41832832176</v>
+        <v>46181.58499498843</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.496993877314</v>
+        <v>46181.663660543985</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>234</v>
@@ -5009,13 +5009,13 @@
         <v>236</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.345439756944</v>
+        <v>46077.512106423615</v>
       </c>
       <c r="C62" s="5">
-        <v>46240.4417334375</v>
+        <v>46240.60840010417</v>
       </c>
       <c r="D62" s="5">
-        <v>46240.441734988424</v>
+        <v>46240.60840165509</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>237</v>
@@ -5058,13 +5058,13 @@
         <v>239</v>
       </c>
       <c r="B63" s="8">
-        <v>46077.34544462963</v>
+        <v>46077.512111296295</v>
       </c>
       <c r="C63" s="8">
-        <v>46240.4413133912</v>
+        <v>46240.607980057874</v>
       </c>
       <c r="D63" s="8">
-        <v>46240.44179618056</v>
+        <v>46240.60846284722</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>240</v>
@@ -5123,13 +5123,13 @@
         <v>243</v>
       </c>
       <c r="B64" s="5">
-        <v>46077.34545173611</v>
+        <v>46077.51211840278</v>
       </c>
       <c r="C64" s="5">
-        <v>46240.44132491898</v>
+        <v>46240.60799158565</v>
       </c>
       <c r="D64" s="5">
-        <v>46240.441820821754</v>
+        <v>46240.608487488425</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>244</v>

--- a/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
+++ b/data/50001504 - ZITRON PERU CODESTABLE A.xlsx
@@ -4578,7 +4578,7 @@
         <v>46181.58491251158</v>
       </c>
       <c r="D55" s="8">
-        <v>46223.819168194445</v>
+        <v>46262.807599328706</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>157</v>
